--- a/dados-catalago-pcm-externo/nomes_usuais.xlsx
+++ b/dados-catalago-pcm-externo/nomes_usuais.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30431"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecas/dados-catalago-pcm-externo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="98" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1832C374-44BE-488F-8C00-C052612CCFA8}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24B53EAF-57A0-492F-AD43-30B5F1B9B991}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4997,7 +4997,7 @@
     </row>
     <row r="306" spans="1:3" ht="15.75">
       <c r="A306" s="12">
-        <v>1010008578</v>
+        <v>1010008637</v>
       </c>
       <c r="B306" s="12" t="s">
         <v>308</v>

--- a/dados-catalago-pcm-externo/nomes_usuais.xlsx
+++ b/dados-catalago-pcm-externo/nomes_usuais.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30431"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecas/dados-catalago-pcm-externo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24B53EAF-57A0-492F-AD43-30B5F1B9B991}"/>
+  <xr:revisionPtr revIDLastSave="108" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28A4B06B-14B7-492E-AA3C-165EBFCAD48F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="382">
   <si>
     <t>material</t>
   </si>
@@ -1179,13 +1179,16 @@
   </si>
   <si>
     <t>TINTA SPRAY AZU 250GR</t>
+  </si>
+  <si>
+    <t>SIRENE DE RÉ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1234,6 +1237,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF374151"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1307,7 +1316,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1351,6 +1360,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1631,15 +1644,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1024"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:G1025"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="59" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1650,7 +1663,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75">
+    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1040019909</v>
       </c>
@@ -1661,7 +1674,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75">
+    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>1040023837</v>
       </c>
@@ -1672,7 +1685,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75">
+    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>1040023836</v>
       </c>
@@ -1683,7 +1696,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75">
+    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>1010000216</v>
       </c>
@@ -1694,7 +1707,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75">
+    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>423651</v>
       </c>
@@ -1705,7 +1718,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75">
+    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>1040077347</v>
       </c>
@@ -1716,7 +1729,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75">
+    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>1040077348</v>
       </c>
@@ -1727,7 +1740,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75">
+    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>417715</v>
       </c>
@@ -1738,7 +1751,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75">
+    <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>1010062075</v>
       </c>
@@ -1749,7 +1762,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75">
+    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>1040083308</v>
       </c>
@@ -1761,7 +1774,7 @@
       </c>
       <c r="G11" s="15"/>
     </row>
-    <row r="12" spans="1:7" ht="15.75">
+    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>1040077346</v>
       </c>
@@ -1772,7 +1785,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15.75">
+    <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>1010049326</v>
       </c>
@@ -1783,7 +1796,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15.75">
+    <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>1040017265</v>
       </c>
@@ -1794,7 +1807,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15.75">
+    <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>1010060188</v>
       </c>
@@ -1805,7 +1818,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15.75">
+    <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>1040019851</v>
       </c>
@@ -1816,7 +1829,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>1010077433</v>
       </c>
@@ -1827,7 +1840,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>1010042610</v>
       </c>
@@ -1838,7 +1851,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>1040077352</v>
       </c>
@@ -1849,7 +1862,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>1040083258</v>
       </c>
@@ -1860,7 +1873,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>68686</v>
       </c>
@@ -1871,7 +1884,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>1010084124</v>
       </c>
@@ -1882,7 +1895,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>102286</v>
       </c>
@@ -1893,7 +1906,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>1010012011</v>
       </c>
@@ -1904,7 +1917,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>1010003651</v>
       </c>
@@ -1915,7 +1928,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>1010062027</v>
       </c>
@@ -1926,7 +1939,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>1010021550</v>
       </c>
@@ -1937,7 +1950,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75">
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>1040077350</v>
       </c>
@@ -1948,7 +1961,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>1040077349</v>
       </c>
@@ -1959,7 +1972,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>13781</v>
       </c>
@@ -1970,7 +1983,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.75">
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>1010058682</v>
       </c>
@@ -1981,7 +1994,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75">
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>1010059706</v>
       </c>
@@ -1992,7 +2005,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.75">
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>1010077386</v>
       </c>
@@ -2003,7 +2016,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75">
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>1010058325</v>
       </c>
@@ -2014,7 +2027,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.75">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>1010061986</v>
       </c>
@@ -2025,7 +2038,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>1040077354</v>
       </c>
@@ -2036,7 +2049,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.75">
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>1010050496</v>
       </c>
@@ -2047,7 +2060,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.75">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>1010050536</v>
       </c>
@@ -2058,7 +2071,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>1010061810</v>
       </c>
@@ -2069,7 +2082,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.75">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>1040092580</v>
       </c>
@@ -2080,7 +2093,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>1010041375</v>
       </c>
@@ -2091,7 +2104,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75">
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>1040098335</v>
       </c>
@@ -2102,7 +2115,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.75">
+    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>1010023362</v>
       </c>
@@ -2113,7 +2126,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.75">
+    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>1010052336</v>
       </c>
@@ -2124,7 +2137,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.75">
+    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>1040077355</v>
       </c>
@@ -2135,7 +2148,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.75">
+    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>230110</v>
       </c>
@@ -2146,7 +2159,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.75">
+    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>1040077357</v>
       </c>
@@ -2157,7 +2170,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.75">
+    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>1040077356</v>
       </c>
@@ -2168,7 +2181,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15.75">
+    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>1040075251</v>
       </c>
@@ -2179,7 +2192,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15.75">
+    <row r="50" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>1040090022</v>
       </c>
@@ -2190,7 +2203,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15.75">
+    <row r="51" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>1010023336</v>
       </c>
@@ -2201,7 +2214,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15.75">
+    <row r="52" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>1010021328</v>
       </c>
@@ -2212,7 +2225,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15.75">
+    <row r="53" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>1010059706</v>
       </c>
@@ -2223,7 +2236,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15.75">
+    <row r="54" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>1010062152</v>
       </c>
@@ -2234,7 +2247,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15.75">
+    <row r="55" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>1040077358</v>
       </c>
@@ -2245,7 +2258,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15.75">
+    <row r="56" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>1010045227</v>
       </c>
@@ -2256,7 +2269,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15.75">
+    <row r="57" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <v>1010085124</v>
       </c>
@@ -2267,7 +2280,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="15.75">
+    <row r="58" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>1010046495</v>
       </c>
@@ -2278,7 +2291,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15.75">
+    <row r="59" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>1040101764</v>
       </c>
@@ -2289,7 +2302,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15.75">
+    <row r="60" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>1010032356</v>
       </c>
@@ -2300,7 +2313,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="15.75">
+    <row r="61" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>428995</v>
       </c>
@@ -2311,7 +2324,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15.75">
+    <row r="62" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>428998</v>
       </c>
@@ -2322,7 +2335,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="15.75">
+    <row r="63" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <v>1040077361</v>
       </c>
@@ -2333,7 +2346,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="15.75">
+    <row r="64" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>1010050445</v>
       </c>
@@ -2344,7 +2357,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="15.75">
+    <row r="65" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>1010050461</v>
       </c>
@@ -2355,7 +2368,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="15.75">
+    <row r="66" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>1010053885</v>
       </c>
@@ -2366,7 +2379,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="15.75">
+    <row r="67" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>1040097102</v>
       </c>
@@ -2377,7 +2390,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="15.75">
+    <row r="68" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>1010020838</v>
       </c>
@@ -2388,7 +2401,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="15.75">
+    <row r="69" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>341430</v>
       </c>
@@ -2399,7 +2412,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="15.75">
+    <row r="70" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>1010042643</v>
       </c>
@@ -2410,7 +2423,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="15.75">
+    <row r="71" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <v>425554</v>
       </c>
@@ -2421,7 +2434,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="15.75">
+    <row r="72" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>224382</v>
       </c>
@@ -2432,7 +2445,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="15.75">
+    <row r="73" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <v>94314</v>
       </c>
@@ -2443,7 +2456,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="15.75">
+    <row r="74" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>1010003982</v>
       </c>
@@ -2454,7 +2467,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="15.75">
+    <row r="75" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <v>1010000182</v>
       </c>
@@ -2465,7 +2478,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="15.75">
+    <row r="76" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>1010021079</v>
       </c>
@@ -2476,7 +2489,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="15.75">
+    <row r="77" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <v>1010002463</v>
       </c>
@@ -2487,7 +2500,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="15.75">
+    <row r="78" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <v>1010062982</v>
       </c>
@@ -2498,7 +2511,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="15.75">
+    <row r="79" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <v>1010063209</v>
       </c>
@@ -2509,7 +2522,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="15.75">
+    <row r="80" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <v>1040076302</v>
       </c>
@@ -2520,7 +2533,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="15.75">
+    <row r="81" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <v>1040077362</v>
       </c>
@@ -2531,7 +2544,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="15.75">
+    <row r="82" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <v>1040077363</v>
       </c>
@@ -2542,7 +2555,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="15.75">
+    <row r="83" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <v>1040074483</v>
       </c>
@@ -2553,7 +2566,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="15.75">
+    <row r="84" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
         <v>1040077364</v>
       </c>
@@ -2564,7 +2577,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="15.75">
+    <row r="85" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <v>1040048463</v>
       </c>
@@ -2575,7 +2588,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="15.75">
+    <row r="86" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <v>1040096343</v>
       </c>
@@ -2586,7 +2599,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="15.75">
+    <row r="87" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="9">
         <v>409640</v>
       </c>
@@ -2597,7 +2610,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="15.75">
+    <row r="88" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
         <v>1010032753</v>
       </c>
@@ -2608,7 +2621,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="15.75">
+    <row r="89" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
         <v>1040098597</v>
       </c>
@@ -2619,7 +2632,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="15.75">
+    <row r="90" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <v>1010007405</v>
       </c>
@@ -2630,7 +2643,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="15.75">
+    <row r="91" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
         <v>1040077365</v>
       </c>
@@ -2641,7 +2654,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="15.75">
+    <row r="92" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
         <v>1010027794</v>
       </c>
@@ -2652,7 +2665,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="15.75">
+    <row r="93" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
         <v>1040077366</v>
       </c>
@@ -2663,7 +2676,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="15.75">
+    <row r="94" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
         <v>1040077367</v>
       </c>
@@ -2674,7 +2687,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="15.75">
+    <row r="95" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="9">
         <v>1010021561</v>
       </c>
@@ -2685,7 +2698,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="15.75">
+    <row r="96" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="9">
         <v>1010021562</v>
       </c>
@@ -2696,7 +2709,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="15.75">
+    <row r="97" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
         <v>1010027792</v>
       </c>
@@ -2707,7 +2720,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="15.75">
+    <row r="98" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
         <v>1010084930</v>
       </c>
@@ -2718,7 +2731,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="15.75">
+    <row r="99" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <v>341430</v>
       </c>
@@ -2729,7 +2742,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="15.75">
+    <row r="100" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
         <v>1010029366</v>
       </c>
@@ -2740,7 +2753,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="15.75">
+    <row r="101" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>1010031723</v>
       </c>
@@ -2751,7 +2764,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="15.75">
+    <row r="102" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
         <v>1010049216</v>
       </c>
@@ -2762,7 +2775,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="15.75">
+    <row r="103" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
         <v>405558</v>
       </c>
@@ -2773,7 +2786,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="15.75">
+    <row r="104" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
         <v>1010023038</v>
       </c>
@@ -2784,7 +2797,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="15.75">
+    <row r="105" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
         <v>1010084109</v>
       </c>
@@ -2795,7 +2808,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="15.75">
+    <row r="106" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
         <v>1010021582</v>
       </c>
@@ -2806,7 +2819,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="15.75">
+    <row r="107" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
         <v>1010021544</v>
       </c>
@@ -2817,7 +2830,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="15.75">
+    <row r="108" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
         <v>1040097133</v>
       </c>
@@ -2828,7 +2841,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="15.75">
+    <row r="109" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="5">
         <v>1040019325</v>
       </c>
@@ -2839,7 +2852,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="15.75">
+    <row r="110" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
         <v>64262</v>
       </c>
@@ -2850,7 +2863,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="15.75">
+    <row r="111" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
         <v>1010047089</v>
       </c>
@@ -2861,7 +2874,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="15.75">
+    <row r="112" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
         <v>1040050168</v>
       </c>
@@ -2872,7 +2885,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="15.75">
+    <row r="113" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
         <v>1040077370</v>
       </c>
@@ -2883,7 +2896,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="15.75">
+    <row r="114" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
         <v>1040099247</v>
       </c>
@@ -2894,7 +2907,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="15.75">
+    <row r="115" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
         <v>1040100560</v>
       </c>
@@ -2905,7 +2918,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="15.75">
+    <row r="116" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
         <v>1040077399</v>
       </c>
@@ -2916,7 +2929,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="15.75">
+    <row r="117" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
         <v>1040077374</v>
       </c>
@@ -2927,7 +2940,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="15.75">
+    <row r="118" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
         <v>1040077399</v>
       </c>
@@ -2938,7 +2951,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="15.75">
+    <row r="119" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="16">
         <v>1010050632</v>
       </c>
@@ -2949,7 +2962,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="15.75">
+    <row r="120" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
         <v>409250</v>
       </c>
@@ -2960,7 +2973,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="15.75">
+    <row r="121" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
         <v>1010020541</v>
       </c>
@@ -2971,7 +2984,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="15.75">
+    <row r="122" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="5">
         <v>1010020879</v>
       </c>
@@ -2982,7 +2995,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="15.75">
+    <row r="123" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
         <v>1040077380</v>
       </c>
@@ -2993,7 +3006,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="15.75">
+    <row r="124" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="5">
         <v>1010021520</v>
       </c>
@@ -3004,7 +3017,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="15.75">
+    <row r="125" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
         <v>1040098861</v>
       </c>
@@ -3015,7 +3028,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="15.75">
+    <row r="126" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="5">
         <v>1010077261</v>
       </c>
@@ -3026,7 +3039,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="15.75">
+    <row r="127" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
         <v>1010027664</v>
       </c>
@@ -3037,7 +3050,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="15.75">
+    <row r="128" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="5">
         <v>1010083731</v>
       </c>
@@ -3048,7 +3061,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="15.75">
+    <row r="129" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" s="5">
         <v>1010083885</v>
       </c>
@@ -3059,7 +3072,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="15.75">
+    <row r="130" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="5">
         <v>1010014834</v>
       </c>
@@ -3070,7 +3083,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="15.75">
+    <row r="131" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="5">
         <v>1010083908</v>
       </c>
@@ -3081,7 +3094,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="15.75">
+    <row r="132" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="5">
         <v>1010024047</v>
       </c>
@@ -3092,7 +3105,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="15.75">
+    <row r="133" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" s="5">
         <v>1040077377</v>
       </c>
@@ -3103,7 +3116,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="15.75">
+    <row r="134" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="5">
         <v>1010061942</v>
       </c>
@@ -3114,7 +3127,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="15.75">
+    <row r="135" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="5">
         <v>1040097070</v>
       </c>
@@ -3125,7 +3138,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="15.75">
+    <row r="136" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="5">
         <v>1040097068</v>
       </c>
@@ -3136,7 +3149,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="15.75">
+    <row r="137" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" s="5">
         <v>1010001010</v>
       </c>
@@ -3147,7 +3160,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="15.75">
+    <row r="138" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="5">
         <v>1010058554</v>
       </c>
@@ -3158,7 +3171,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="15.75">
+    <row r="139" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="5">
         <v>1010027308</v>
       </c>
@@ -3169,7 +3182,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="15.75">
+    <row r="140" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="5">
         <v>1040077383</v>
       </c>
@@ -3180,7 +3193,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="15.75">
+    <row r="141" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="5">
         <v>1010025482</v>
       </c>
@@ -3191,7 +3204,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="15.75">
+    <row r="142" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="5">
         <v>1010025509</v>
       </c>
@@ -3202,7 +3215,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="15.75">
+    <row r="143" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="5">
         <v>1010027789</v>
       </c>
@@ -3213,7 +3226,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="15.75">
+    <row r="144" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" s="5">
         <v>1010027790</v>
       </c>
@@ -3224,7 +3237,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="15.75">
+    <row r="145" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" s="5">
         <v>1010020758</v>
       </c>
@@ -3235,7 +3248,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="15.75">
+    <row r="146" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" s="5">
         <v>1010020781</v>
       </c>
@@ -3246,7 +3259,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="15.75">
+    <row r="147" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="5">
         <v>1010058426</v>
       </c>
@@ -3257,7 +3270,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="15.75">
+    <row r="148" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="5">
         <v>1010059332</v>
       </c>
@@ -3268,7 +3281,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="15.75">
+    <row r="149" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="5">
         <v>1040077389</v>
       </c>
@@ -3279,7 +3292,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="15.75">
+    <row r="150" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="5">
         <v>1010021364</v>
       </c>
@@ -3290,7 +3303,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="15.75">
+    <row r="151" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="5">
         <v>1010021541</v>
       </c>
@@ -3301,7 +3314,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="15.75">
+    <row r="152" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="5">
         <v>1010021955</v>
       </c>
@@ -3312,7 +3325,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="15.75">
+    <row r="153" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="5">
         <v>1040077388</v>
       </c>
@@ -3323,7 +3336,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="15.75">
+    <row r="154" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" s="5">
         <v>1010058100</v>
       </c>
@@ -3334,7 +3347,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="15.75">
+    <row r="155" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" s="5">
         <v>1010020524</v>
       </c>
@@ -3345,7 +3358,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="15.75">
+    <row r="156" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" s="5">
         <v>1010021958</v>
       </c>
@@ -3356,7 +3369,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="15.75">
+    <row r="157" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" s="5">
         <v>1010019756</v>
       </c>
@@ -3367,7 +3380,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="15.75">
+    <row r="158" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" s="9">
         <v>1010019752</v>
       </c>
@@ -3378,7 +3391,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="15.75">
+    <row r="159" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" s="5">
         <v>409639</v>
       </c>
@@ -3389,7 +3402,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="15.75">
+    <row r="160" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" s="9">
         <v>1010047089</v>
       </c>
@@ -3400,7 +3413,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="15.75">
+    <row r="161" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" s="9">
         <v>1040084107</v>
       </c>
@@ -3411,7 +3424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="15.75">
+    <row r="162" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" s="5">
         <v>1010085203</v>
       </c>
@@ -3422,7 +3435,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="15.75">
+    <row r="163" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" s="5">
         <v>424298</v>
       </c>
@@ -3433,7 +3446,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="15.75">
+    <row r="164" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" s="5">
         <v>421847</v>
       </c>
@@ -3444,7 +3457,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="15.75">
+    <row r="165" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" s="5">
         <v>431573</v>
       </c>
@@ -3455,7 +3468,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="15.75">
+    <row r="166" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" s="5">
         <v>1010021581</v>
       </c>
@@ -3466,7 +3479,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="15.75">
+    <row r="167" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" s="5">
         <v>1040077390</v>
       </c>
@@ -3477,7 +3490,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="15.75">
+    <row r="168" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" s="5">
         <v>1010021542</v>
       </c>
@@ -3488,7 +3501,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="15.75">
+    <row r="169" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" s="5">
         <v>1010021733</v>
       </c>
@@ -3499,7 +3512,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="15.75">
+    <row r="170" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" s="5">
         <v>1010021929</v>
       </c>
@@ -3510,7 +3523,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="15.75">
+    <row r="171" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" s="5">
         <v>428065</v>
       </c>
@@ -3521,7 +3534,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="15.75">
+    <row r="172" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="5">
         <v>1010003404</v>
       </c>
@@ -3532,7 +3545,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="15.75">
+    <row r="173" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" s="5">
         <v>1010003322</v>
       </c>
@@ -3543,7 +3556,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="15.75">
+    <row r="174" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" s="5">
         <v>17738</v>
       </c>
@@ -3554,7 +3567,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="15.75">
+    <row r="175" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" s="5">
         <v>1010085360</v>
       </c>
@@ -3565,7 +3578,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="15.75">
+    <row r="176" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" s="5">
         <v>1040077391</v>
       </c>
@@ -3576,7 +3589,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="15.75">
+    <row r="177" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="5">
         <v>1010058624</v>
       </c>
@@ -3587,7 +3600,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="15.75">
+    <row r="178" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="5">
         <v>1010024661</v>
       </c>
@@ -3598,7 +3611,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="15.75">
+    <row r="179" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" s="5">
         <v>1040019315</v>
       </c>
@@ -3609,7 +3622,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="15.75">
+    <row r="180" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="5">
         <v>1010021089</v>
       </c>
@@ -3620,7 +3633,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="15.75">
+    <row r="181" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="5">
         <v>1040017264</v>
       </c>
@@ -3631,7 +3644,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="15.75">
+    <row r="182" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" s="5">
         <v>1010051765</v>
       </c>
@@ -3642,7 +3655,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="15.75">
+    <row r="183" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="5">
         <v>1010035272</v>
       </c>
@@ -3653,7 +3666,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="15.75">
+    <row r="184" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="5">
         <v>1040077392</v>
       </c>
@@ -3664,7 +3677,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="15.75">
+    <row r="185" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" s="5">
         <v>1040077393</v>
       </c>
@@ -3675,7 +3688,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="15.75">
+    <row r="186" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" s="5">
         <v>1040077395</v>
       </c>
@@ -3686,7 +3699,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="15.75">
+    <row r="187" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="5">
         <v>1040077401</v>
       </c>
@@ -3697,7 +3710,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="15.75">
+    <row r="188" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="5">
         <v>27572</v>
       </c>
@@ -3708,7 +3721,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="15.75">
+    <row r="189" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" s="5">
         <v>18745</v>
       </c>
@@ -3719,7 +3732,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="15.75">
+    <row r="190" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" s="5">
         <v>1040077396</v>
       </c>
@@ -3730,7 +3743,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="15.75">
+    <row r="191" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" s="5">
         <v>1010036546</v>
       </c>
@@ -3741,7 +3754,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="15.75">
+    <row r="192" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="5">
         <v>1010025148</v>
       </c>
@@ -3752,7 +3765,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="15.75">
+    <row r="193" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" s="5">
         <v>1040077394</v>
       </c>
@@ -3763,7 +3776,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="15.75">
+    <row r="194" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="5">
         <v>1040077400</v>
       </c>
@@ -3774,7 +3787,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="15.75">
+    <row r="195" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" s="5">
         <v>1040079329</v>
       </c>
@@ -3785,7 +3798,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="15.75">
+    <row r="196" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" s="9">
         <v>1040040957</v>
       </c>
@@ -3796,7 +3809,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="15.75">
+    <row r="197" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" s="5">
         <v>1040077398</v>
       </c>
@@ -3807,7 +3820,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="15.75">
+    <row r="198" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" s="5">
         <v>1010020554</v>
       </c>
@@ -3818,7 +3831,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="15.75">
+    <row r="199" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" s="5">
         <v>1040085949</v>
       </c>
@@ -3829,7 +3842,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="15.75">
+    <row r="200" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" s="5">
         <v>1010062938</v>
       </c>
@@ -3840,7 +3853,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="15.75">
+    <row r="201" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" s="5">
         <v>1010062086</v>
       </c>
@@ -3851,7 +3864,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="15.75">
+    <row r="202" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" s="5">
         <v>1010062087</v>
       </c>
@@ -3862,7 +3875,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="15.75">
+    <row r="203" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" s="5">
         <v>1040077373</v>
       </c>
@@ -3873,7 +3886,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="15.75">
+    <row r="204" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" s="5">
         <v>1040077372</v>
       </c>
@@ -3884,7 +3897,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="15.75">
+    <row r="205" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" s="10">
         <v>1040097154</v>
       </c>
@@ -3895,7 +3908,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="15.75">
+    <row r="206" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" s="10">
         <v>1010042579</v>
       </c>
@@ -3906,7 +3919,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="15.75">
+    <row r="207" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" s="10">
         <v>1010029427</v>
       </c>
@@ -3917,7 +3930,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="15.75">
+    <row r="208" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" s="5">
         <v>133108</v>
       </c>
@@ -3928,7 +3941,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="15.75">
+    <row r="209" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" s="16">
         <v>269427</v>
       </c>
@@ -3939,7 +3952,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="15.75">
+    <row r="210" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" s="5">
         <v>298227</v>
       </c>
@@ -3950,7 +3963,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="15.75">
+    <row r="211" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" s="5">
         <v>1010062285</v>
       </c>
@@ -3961,7 +3974,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="15.75">
+    <row r="212" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" s="5">
         <v>1010058052</v>
       </c>
@@ -3972,7 +3985,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="15.75">
+    <row r="213" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" s="5">
         <v>1010050033</v>
       </c>
@@ -3983,7 +3996,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="15.75">
+    <row r="214" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" s="5">
         <v>1040098869</v>
       </c>
@@ -3994,7 +4007,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="15.75">
+    <row r="215" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" s="5">
         <v>1010056523</v>
       </c>
@@ -4005,7 +4018,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="15.75">
+    <row r="216" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" s="5">
         <v>1010062045</v>
       </c>
@@ -4016,7 +4029,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="15.75">
+    <row r="217" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" s="5">
         <v>1040097575</v>
       </c>
@@ -4027,7 +4040,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="15.75">
+    <row r="218" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" s="5">
         <v>1040100107</v>
       </c>
@@ -4038,7 +4051,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="15.75">
+    <row r="219" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" s="5">
         <v>1010040346</v>
       </c>
@@ -4049,7 +4062,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="15.75">
+    <row r="220" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" s="5">
         <v>1010021543</v>
       </c>
@@ -4060,7 +4073,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="15.75">
+    <row r="221" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" s="5">
         <v>1040077397</v>
       </c>
@@ -4071,7 +4084,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="15.75">
+    <row r="222" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" s="5">
         <v>1040094213</v>
       </c>
@@ -4082,7 +4095,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="15.75">
+    <row r="223" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" s="5">
         <v>1010042564</v>
       </c>
@@ -4093,7 +4106,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="15.75">
+    <row r="224" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" s="5">
         <v>1010042688</v>
       </c>
@@ -4104,7 +4117,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="15.75">
+    <row r="225" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" s="5">
         <v>1010040133</v>
       </c>
@@ -4115,7 +4128,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="15.75">
+    <row r="226" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" s="5">
         <v>1010039879</v>
       </c>
@@ -4126,7 +4139,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="15.75">
+    <row r="227" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" s="5">
         <v>62608</v>
       </c>
@@ -4137,7 +4150,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="15.75">
+    <row r="228" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" s="5">
         <v>1040098603</v>
       </c>
@@ -4148,7 +4161,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="15.75">
+    <row r="229" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" s="5">
         <v>1040017266</v>
       </c>
@@ -4159,7 +4172,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="15.75">
+    <row r="230" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" s="5">
         <v>1010063326</v>
       </c>
@@ -4170,7 +4183,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="15.75">
+    <row r="231" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" s="5">
         <v>1010050574</v>
       </c>
@@ -4181,7 +4194,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="15.75">
+    <row r="232" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" s="5">
         <v>1010086126</v>
       </c>
@@ -4192,7 +4205,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="15.75">
+    <row r="233" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" s="5">
         <v>1040019838</v>
       </c>
@@ -4203,7 +4216,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="15.75">
+    <row r="234" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" s="5">
         <v>1010042882</v>
       </c>
@@ -4214,7 +4227,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="15.75">
+    <row r="235" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" s="5">
         <v>1010042873</v>
       </c>
@@ -4225,7 +4238,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="15.75">
+    <row r="236" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" s="5">
         <v>1010026842</v>
       </c>
@@ -4236,7 +4249,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="15.75">
+    <row r="237" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" s="5">
         <v>1010026841</v>
       </c>
@@ -4247,7 +4260,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="15.75">
+    <row r="238" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" s="5">
         <v>1010059549</v>
       </c>
@@ -4258,7 +4271,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="15.75">
+    <row r="239" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" s="5">
         <v>1010020552</v>
       </c>
@@ -4269,7 +4282,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="15.75">
+    <row r="240" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" s="5">
         <v>1040078895</v>
       </c>
@@ -4280,7 +4293,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="15.75">
+    <row r="241" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" s="5">
         <v>1040024309</v>
       </c>
@@ -4291,7 +4304,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="15.75">
+    <row r="242" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" s="5">
         <v>1040024323</v>
       </c>
@@ -4302,7 +4315,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="15.75">
+    <row r="243" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" s="5">
         <v>1040024322</v>
       </c>
@@ -4313,7 +4326,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="15.75">
+    <row r="244" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" s="5">
         <v>1010087245</v>
       </c>
@@ -4324,7 +4337,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="15.75">
+    <row r="245" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" s="5">
         <v>1010059685</v>
       </c>
@@ -4335,7 +4348,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="15.75">
+    <row r="246" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" s="5">
         <v>1010059687</v>
       </c>
@@ -4346,7 +4359,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="15.75">
+    <row r="247" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" s="7">
         <v>1010077469</v>
       </c>
@@ -4357,7 +4370,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="15.75">
+    <row r="248" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" s="5">
         <v>1010077470</v>
       </c>
@@ -4368,7 +4381,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="15.75">
+    <row r="249" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" s="5">
         <v>1010084519</v>
       </c>
@@ -4379,7 +4392,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="15.75">
+    <row r="250" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" s="5">
         <v>1010084108</v>
       </c>
@@ -4390,7 +4403,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="15.75">
+    <row r="251" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" s="5">
         <v>1010042884</v>
       </c>
@@ -4401,7 +4414,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="15.75">
+    <row r="252" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" s="5">
         <v>1040043537</v>
       </c>
@@ -4412,7 +4425,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="253" spans="1:3" ht="15.75">
+    <row r="253" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" s="5">
         <v>1010046401</v>
       </c>
@@ -4423,7 +4436,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="254" spans="1:3" ht="15.75">
+    <row r="254" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" s="5">
         <v>1010062007</v>
       </c>
@@ -4434,7 +4447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="15.75">
+    <row r="255" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" s="5">
         <v>1010051284</v>
       </c>
@@ -4445,7 +4458,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="256" spans="1:3" ht="15.75">
+    <row r="256" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" s="5">
         <v>1010027788</v>
       </c>
@@ -4456,7 +4469,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="15.75">
+    <row r="257" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" s="5">
         <v>1010027786</v>
       </c>
@@ -4467,7 +4480,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="15.75">
+    <row r="258" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" s="5">
         <v>1040023848</v>
       </c>
@@ -4478,7 +4491,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="15.75">
+    <row r="259" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" s="5">
         <v>1040098396</v>
       </c>
@@ -4489,7 +4502,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="260" spans="1:3" ht="15.75">
+    <row r="260" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" s="5">
         <v>1010087281</v>
       </c>
@@ -4500,7 +4513,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="261" spans="1:3" ht="15.75">
+    <row r="261" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" s="5">
         <v>1040041006</v>
       </c>
@@ -4511,7 +4524,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="15.75">
+    <row r="262" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" s="5">
         <v>1040101931</v>
       </c>
@@ -4522,7 +4535,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="15.75">
+    <row r="263" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" s="5">
         <v>1040023843</v>
       </c>
@@ -4533,7 +4546,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="15.75">
+    <row r="264" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" s="5">
         <v>1040077411</v>
       </c>
@@ -4544,7 +4557,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:3" ht="15.75">
+    <row r="265" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" s="5">
         <v>1040077410</v>
       </c>
@@ -4555,7 +4568,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="266" spans="1:3" ht="15.75">
+    <row r="266" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" s="5">
         <v>1010062008</v>
       </c>
@@ -4566,7 +4579,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="267" spans="1:3" ht="15.75">
+    <row r="267" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" s="5">
         <v>1040040960</v>
       </c>
@@ -4577,7 +4590,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="1:3" ht="15.75">
+    <row r="268" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" s="5">
         <v>1040077360</v>
       </c>
@@ -4588,7 +4601,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="269" spans="1:3" ht="15.75">
+    <row r="269" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" s="5">
         <v>1010064470</v>
       </c>
@@ -4599,7 +4612,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="270" spans="1:3" ht="15.75">
+    <row r="270" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" s="5">
         <v>1010021991</v>
       </c>
@@ -4610,7 +4623,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="271" spans="1:3" ht="15.75">
+    <row r="271" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="11">
         <v>1010021960</v>
       </c>
@@ -4621,7 +4634,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="15.75">
+    <row r="272" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" s="5">
         <v>1010022590</v>
       </c>
@@ -4632,7 +4645,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="273" spans="1:3" ht="15.75">
+    <row r="273" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" s="5">
         <v>1040098643</v>
       </c>
@@ -4643,7 +4656,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="15.75">
+    <row r="274" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" s="5">
         <v>1010086020</v>
       </c>
@@ -4654,7 +4667,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="275" spans="1:3" ht="15.75">
+    <row r="275" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" s="5">
         <v>1010046550</v>
       </c>
@@ -4665,7 +4678,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="15.75">
+    <row r="276" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" s="5">
         <v>1010046402</v>
       </c>
@@ -4676,7 +4689,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="277" spans="1:3" ht="15.75">
+    <row r="277" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" s="5">
         <v>1010060291</v>
       </c>
@@ -4687,7 +4700,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="278" spans="1:3" ht="15.75">
+    <row r="278" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" s="5">
         <v>1010050920</v>
       </c>
@@ -4698,7 +4711,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="279" spans="1:3" ht="15.75">
+    <row r="279" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" s="5">
         <v>1040077412</v>
       </c>
@@ -4709,7 +4722,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="280" spans="1:3" ht="15.75">
+    <row r="280" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280" s="5">
         <v>1010042609</v>
       </c>
@@ -4720,7 +4733,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="281" spans="1:3" ht="15.75">
+    <row r="281" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" s="5">
         <v>417701</v>
       </c>
@@ -4731,7 +4744,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="282" spans="1:3" ht="15.75">
+    <row r="282" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" s="5">
         <v>399384</v>
       </c>
@@ -4742,7 +4755,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="283" spans="1:3" ht="15.75">
+    <row r="283" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" s="5">
         <v>1010024086</v>
       </c>
@@ -4753,7 +4766,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="284" spans="1:3" ht="15.75">
+    <row r="284" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" s="5">
         <v>1040077345</v>
       </c>
@@ -4764,7 +4777,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="285" spans="1:3" ht="15.75">
+    <row r="285" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" s="16">
         <v>1040077368</v>
       </c>
@@ -4775,7 +4788,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="1:3" ht="15.75">
+    <row r="286" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" s="5">
         <v>399253</v>
       </c>
@@ -4786,7 +4799,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="1:3" ht="15.75">
+    <row r="287" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" s="5">
         <v>1010084317</v>
       </c>
@@ -4797,7 +4810,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="288" spans="1:3" ht="15.75">
+    <row r="288" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" s="12">
         <v>1010085369</v>
       </c>
@@ -4808,7 +4821,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="289" spans="1:3" ht="15.75">
+    <row r="289" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" s="12">
         <v>1010085370</v>
       </c>
@@ -4819,7 +4832,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="290" spans="1:3" ht="15.75">
+    <row r="290" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" s="12">
         <v>1010085204</v>
       </c>
@@ -4830,7 +4843,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="1:3" ht="15.75">
+    <row r="291" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" s="12">
         <v>1010003966</v>
       </c>
@@ -4841,7 +4854,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="292" spans="1:3" ht="15.75">
+    <row r="292" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" s="12">
         <v>1010003967</v>
       </c>
@@ -4852,7 +4865,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="293" spans="1:3" ht="15.75">
+    <row r="293" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" s="12">
         <v>65219</v>
       </c>
@@ -4863,7 +4876,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="294" spans="1:3" ht="15.75">
+    <row r="294" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" s="12">
         <v>10168</v>
       </c>
@@ -4874,7 +4887,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="295" spans="1:3" ht="15.75">
+    <row r="295" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" s="12">
         <v>1010083792</v>
       </c>
@@ -4885,7 +4898,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="296" spans="1:3" ht="15.75">
+    <row r="296" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" s="12">
         <v>1040077414</v>
       </c>
@@ -4896,7 +4909,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="297" spans="1:3" ht="15.75">
+    <row r="297" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297" s="13">
         <v>1010018482</v>
       </c>
@@ -4907,7 +4920,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="298" spans="1:3" ht="15.75">
+    <row r="298" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" s="13">
         <v>1010084320</v>
       </c>
@@ -4918,7 +4931,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="299" spans="1:3" ht="15.75">
+    <row r="299" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" s="12">
         <v>1010084532</v>
       </c>
@@ -4929,7 +4942,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="300" spans="1:3" ht="15.75">
+    <row r="300" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" s="12">
         <v>1010027285</v>
       </c>
@@ -4940,7 +4953,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="301" spans="1:3" ht="15.75">
+    <row r="301" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" s="12">
         <v>1040077413</v>
       </c>
@@ -4951,7 +4964,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="302" spans="1:3" ht="15.75">
+    <row r="302" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" s="12">
         <v>1010085376</v>
       </c>
@@ -4962,7 +4975,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="303" spans="1:3" ht="15.75">
+    <row r="303" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" s="12">
         <v>1010022819</v>
       </c>
@@ -4973,7 +4986,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="304" spans="1:3" ht="15.75">
+    <row r="304" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" s="12">
         <v>1010052853</v>
       </c>
@@ -4984,3383 +4997,3396 @@
         <v>4</v>
       </c>
     </row>
-    <row r="305" spans="1:3" ht="15.75">
+    <row r="305" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A305" s="12">
+        <v>1010006162</v>
+      </c>
+      <c r="B305" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="C305" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A306" s="12">
         <v>1010084377</v>
       </c>
-      <c r="B305" s="12" t="s">
+      <c r="B306" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="C305" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" ht="15.75">
-      <c r="A306" s="12">
+      <c r="C306" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F306" s="15"/>
+    </row>
+    <row r="307" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A307" s="12">
         <v>1010008637</v>
       </c>
-      <c r="B306" s="12" t="s">
+      <c r="B307" s="12" t="s">
         <v>308</v>
-      </c>
-      <c r="C306" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3" ht="15.75">
-      <c r="A307" s="12">
-        <v>1010031694</v>
-      </c>
-      <c r="B307" s="12" t="s">
-        <v>310</v>
       </c>
       <c r="C307" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="308" spans="1:3" ht="15.75">
+    <row r="308" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" s="12">
-        <v>1010051997</v>
+        <v>1010031694</v>
       </c>
       <c r="B308" s="12" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C308" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="309" spans="1:3" ht="15.75">
+    <row r="309" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" s="12">
-        <v>1010022601</v>
+        <v>1010051997</v>
       </c>
       <c r="B309" s="12" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C309" s="6" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="310" spans="1:3" ht="15.75">
+      <c r="F309" s="18"/>
+    </row>
+    <row r="310" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" s="12">
-        <v>1010084144</v>
+        <v>1010022601</v>
       </c>
       <c r="B310" s="12" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C310" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="311" spans="1:3" ht="15.75">
+    <row r="311" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" s="12">
-        <v>1010084958</v>
+        <v>1010084144</v>
       </c>
       <c r="B311" s="12" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C311" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="312" spans="1:3" ht="15.75">
+    <row r="312" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" s="12">
-        <v>1010021956</v>
-      </c>
-      <c r="B312" s="14" t="s">
-        <v>315</v>
+        <v>1010084958</v>
+      </c>
+      <c r="B312" s="12" t="s">
+        <v>314</v>
       </c>
       <c r="C312" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="313" spans="1:3" ht="15.75">
+    <row r="313" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" s="12">
-        <v>1010026464</v>
-      </c>
-      <c r="B313" s="12" t="s">
-        <v>316</v>
+        <v>1010021956</v>
+      </c>
+      <c r="B313" s="14" t="s">
+        <v>315</v>
       </c>
       <c r="C313" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="314" spans="1:3" ht="15.75">
+    <row r="314" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" s="12">
-        <v>1010021957</v>
+        <v>1010026464</v>
       </c>
       <c r="B314" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C314" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="315" spans="1:3" ht="15.75">
+    <row r="315" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" s="12">
-        <v>1010026462</v>
+        <v>1010021957</v>
       </c>
       <c r="B315" s="12" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C315" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="316" spans="1:3" ht="15.75">
+    <row r="316" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" s="12">
-        <v>1010026551</v>
+        <v>1010026462</v>
       </c>
       <c r="B316" s="12" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C316" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="317" spans="1:3" ht="15.75">
+    <row r="317" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" s="12">
-        <v>1010042554</v>
+        <v>1010026551</v>
       </c>
       <c r="B317" s="12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C317" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="318" spans="1:3" ht="15.75">
+    <row r="318" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" s="12">
-        <v>1010039904</v>
+        <v>1010042554</v>
       </c>
       <c r="B318" s="12" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C318" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="319" spans="1:3" ht="15.75">
+    <row r="319" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" s="12">
-        <v>1010060205</v>
+        <v>1010039904</v>
       </c>
       <c r="B319" s="12" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C319" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="320" spans="1:3" ht="15.75">
+    <row r="320" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" s="12">
-        <v>1010060206</v>
+        <v>1010060205</v>
       </c>
       <c r="B320" s="12" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C320" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="321" spans="1:3" ht="15.75">
+    <row r="321" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" s="12">
-        <v>1010077431</v>
+        <v>1010060206</v>
       </c>
       <c r="B321" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C321" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="322" spans="1:3" ht="15.75">
+    <row r="322" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" s="12">
-        <v>1010077503</v>
+        <v>1010077431</v>
       </c>
       <c r="B322" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C322" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="323" spans="1:3" ht="15.75">
+    <row r="323" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" s="12">
-        <v>1010026032</v>
+        <v>1010077503</v>
       </c>
       <c r="B323" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C323" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="324" spans="1:3" ht="15.75">
+    <row r="324" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" s="12">
-        <v>1010006347</v>
+        <v>1010026032</v>
       </c>
       <c r="B324" s="12" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C324" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="325" spans="1:3" ht="15.75">
+    <row r="325" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" s="12">
-        <v>1010085179</v>
+        <v>1010006347</v>
       </c>
       <c r="B325" s="12" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C325" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="326" spans="1:3" ht="15.75">
+    <row r="326" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" s="12">
-        <v>1010024158</v>
+        <v>1010085179</v>
       </c>
       <c r="B326" s="12" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C326" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="327" spans="1:3" ht="15.75">
+    <row r="327" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" s="12">
-        <v>1010024131</v>
+        <v>1010024158</v>
       </c>
       <c r="B327" s="12" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C327" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="328" spans="1:3" ht="15.75">
+    <row r="328" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" s="12">
-        <v>1010007160</v>
+        <v>1010024131</v>
       </c>
       <c r="B328" s="12" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C328" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="329" spans="1:3" ht="15.75">
+    <row r="329" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" s="12">
-        <v>1010023642</v>
+        <v>1010007160</v>
       </c>
       <c r="B329" s="12" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C329" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="330" spans="1:3" ht="15.75">
+    <row r="330" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" s="12">
-        <v>1010007193</v>
+        <v>1010023642</v>
       </c>
       <c r="B330" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C330" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="331" spans="1:3" ht="15.75">
+    <row r="331" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" s="12">
-        <v>1010042637</v>
+        <v>1010007193</v>
       </c>
       <c r="B331" s="12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C331" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="332" spans="1:3" ht="15.75">
+    <row r="332" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" s="12">
-        <v>1040075323</v>
+        <v>1010042637</v>
       </c>
       <c r="B332" s="12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C332" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="333" spans="1:3" ht="15.75">
+    <row r="333" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" s="12">
-        <v>1040075324</v>
+        <v>1040075323</v>
       </c>
       <c r="B333" s="12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C333" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="334" spans="1:3" ht="15.75">
+    <row r="334" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" s="12">
-        <v>1040074827</v>
+        <v>1040075324</v>
       </c>
       <c r="B334" s="12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C334" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="335" spans="1:3" ht="15.75">
+    <row r="335" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" s="12">
-        <v>1040099488</v>
+        <v>1040074827</v>
       </c>
       <c r="B335" s="12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C335" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="336" spans="1:3" ht="15.75">
+    <row r="336" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" s="12">
-        <v>1040083312</v>
+        <v>1040099488</v>
       </c>
       <c r="B336" s="12" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C336" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="337" spans="1:5" ht="15.75">
-      <c r="A337" s="8">
-        <v>1040077661</v>
-      </c>
-      <c r="B337" s="8" t="s">
-        <v>340</v>
+    <row r="337" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A337" s="12">
+        <v>1040083312</v>
+      </c>
+      <c r="B337" s="12" t="s">
+        <v>339</v>
       </c>
       <c r="C337" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="338" spans="1:5" ht="15.75">
+    <row r="338" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" s="8">
-        <v>1010085180</v>
+        <v>1040077661</v>
       </c>
       <c r="B338" s="8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C338" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="339" spans="1:5" ht="15.75">
+    <row r="339" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" s="8">
-        <v>1040017489</v>
+        <v>1010085180</v>
       </c>
       <c r="B339" s="8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C339" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="340" spans="1:5" ht="15.75">
+    <row r="340" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" s="8">
-        <v>1010085181</v>
+        <v>1040017489</v>
       </c>
       <c r="B340" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C340" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="341" spans="1:5" ht="15.75">
+    <row r="341" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" s="8">
-        <v>400175</v>
+        <v>1010085181</v>
       </c>
       <c r="B341" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C341" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="342" spans="1:5" ht="15.75">
+    <row r="342" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" s="8">
-        <v>1040017505</v>
+        <v>400175</v>
       </c>
       <c r="B342" s="8" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C342" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="343" spans="1:5" ht="15.75">
+    <row r="343" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" s="8">
-        <v>1040017503</v>
+        <v>1040017505</v>
       </c>
       <c r="B343" s="8" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C343" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="344" spans="1:5" ht="15.75">
+    <row r="344" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" s="8">
-        <v>1010046445</v>
+        <v>1040017503</v>
       </c>
       <c r="B344" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C344" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="E344" s="15"/>
-    </row>
-    <row r="345" spans="1:5" ht="15.75">
+    </row>
+    <row r="345" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" s="8">
-        <v>1010021033</v>
+        <v>1010046445</v>
       </c>
       <c r="B345" s="8" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C345" s="6" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="346" spans="1:5" ht="15.75">
+      <c r="E345" s="15"/>
+    </row>
+    <row r="346" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" s="8">
-        <v>1010016356</v>
+        <v>1010021033</v>
       </c>
       <c r="B346" s="8" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C346" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="347" spans="1:5" ht="15.75">
+    <row r="347" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" s="8">
-        <v>1010084363</v>
+        <v>1010016356</v>
       </c>
       <c r="B347" s="8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C347" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="348" spans="1:5" ht="15.75">
+    <row r="348" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" s="8">
-        <v>1010052021</v>
+        <v>1010084363</v>
       </c>
       <c r="B348" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C348" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="349" spans="1:5" ht="15.75">
+    <row r="349" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" s="8">
-        <v>1040091721</v>
+        <v>1010052021</v>
       </c>
       <c r="B349" s="8" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C349" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="350" spans="1:5" ht="15.75">
+    <row r="350" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" s="8">
-        <v>1010062022</v>
+        <v>1040091721</v>
       </c>
       <c r="B350" s="8" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C350" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="351" spans="1:5" ht="15.75">
+    <row r="351" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" s="8">
-        <v>18336</v>
+        <v>1010062022</v>
       </c>
       <c r="B351" s="8" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C351" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="352" spans="1:5" ht="15.75">
+    <row r="352" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" s="8">
-        <v>229205</v>
+        <v>18336</v>
       </c>
       <c r="B352" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C352" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="353" spans="1:3" ht="15.75">
+    <row r="353" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" s="8">
-        <v>1010059726</v>
+        <v>229205</v>
       </c>
       <c r="B353" s="8" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C353" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="354" spans="1:3" ht="15.75">
+    <row r="354" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" s="8">
-        <v>1010008144</v>
+        <v>1010059726</v>
       </c>
       <c r="B354" s="8" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C354" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="355" spans="1:3" ht="15.75">
+    <row r="355" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" s="8">
-        <v>1010007244</v>
+        <v>1010008144</v>
       </c>
       <c r="B355" s="8" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C355" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="356" spans="1:3" ht="15.75">
+    <row r="356" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" s="8">
-        <v>1010006827</v>
+        <v>1010007244</v>
       </c>
       <c r="B356" s="8" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C356" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="357" spans="1:3" ht="15.75">
+    <row r="357" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" s="8">
-        <v>1040075426</v>
+        <v>1010006827</v>
       </c>
       <c r="B357" s="8" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C357" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="358" spans="1:3" ht="15.75">
+    <row r="358" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" s="8">
-        <v>1040075427</v>
+        <v>1040075426</v>
       </c>
       <c r="B358" s="8" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C358" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="359" spans="1:3" ht="15.75">
+    <row r="359" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" s="8">
-        <v>1010084313</v>
+        <v>1040075427</v>
       </c>
       <c r="B359" s="8" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C359" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="360" spans="1:3" ht="15.75">
+    <row r="360" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" s="8">
-        <v>403459</v>
+        <v>1010084313</v>
       </c>
       <c r="B360" s="8" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C360" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="361" spans="1:3" ht="15.75">
+    <row r="361" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" s="8">
-        <v>1010044828</v>
+        <v>403459</v>
       </c>
       <c r="B361" s="8" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C361" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="362" spans="1:3" ht="15.75">
+    <row r="362" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" s="8">
-        <v>1010026973</v>
+        <v>1010044828</v>
       </c>
       <c r="B362" s="8" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C362" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="363" spans="1:3" ht="15.75">
+    <row r="363" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" s="8">
-        <v>1040017204</v>
+        <v>1010026973</v>
       </c>
       <c r="B363" s="8" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C363" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="364" spans="1:3" ht="15.75">
+    <row r="364" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" s="8">
+        <v>1040017204</v>
+      </c>
+      <c r="B364" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="C364" s="6" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A365" s="8">
         <v>1010022588</v>
       </c>
-      <c r="B364" s="8" t="s">
+      <c r="B365" s="8" t="s">
         <v>367</v>
-      </c>
-      <c r="C364" s="6" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="365" spans="1:3" ht="15.75">
-      <c r="A365" s="8">
-        <v>1010026864</v>
-      </c>
-      <c r="B365" s="8" t="s">
-        <v>369</v>
       </c>
       <c r="C365" s="6" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="366" spans="1:3" ht="15.75">
+    <row r="366" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" s="8">
-        <v>1010030946</v>
+        <v>1010026864</v>
       </c>
       <c r="B366" s="8" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C366" s="6" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="367" spans="1:3" ht="15.75">
+    <row r="367" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" s="8">
-        <v>1010022589</v>
+        <v>1010030946</v>
       </c>
       <c r="B367" s="8" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C367" s="6" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="368" spans="1:3" ht="15.75">
+    <row r="368" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" s="8">
-        <v>1040090143</v>
+        <v>1010022589</v>
       </c>
       <c r="B368" s="8" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C368" s="6" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="369" spans="1:3" ht="15.75">
+    <row r="369" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" s="8">
-        <v>1040090138</v>
+        <v>1040090143</v>
       </c>
       <c r="B369" s="8" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C369" s="6" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="370" spans="1:3" ht="15.75">
+    <row r="370" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" s="8">
+        <v>1040090138</v>
+      </c>
+      <c r="B370" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="C370" s="6" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A371" s="8">
         <v>1010084195</v>
       </c>
-      <c r="B370" s="8" t="s">
+      <c r="B371" s="8" t="s">
         <v>374</v>
-      </c>
-      <c r="C370" s="6" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="371" spans="1:3" ht="15.75">
-      <c r="A371" s="8">
-        <v>1010001400</v>
-      </c>
-      <c r="B371" s="8" t="s">
-        <v>376</v>
       </c>
       <c r="C371" s="6" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="372" spans="1:3" ht="15.75">
+    <row r="372" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" s="8">
-        <v>1010008416</v>
+        <v>1010001400</v>
       </c>
       <c r="B372" s="8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C372" s="6" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="373" spans="1:3" ht="15.75">
+    <row r="373" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" s="8">
-        <v>1010000896</v>
+        <v>1010008416</v>
       </c>
       <c r="B373" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C373" s="6" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="374" spans="1:3" ht="15.75">
+    <row r="374" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" s="8">
-        <v>1010084308</v>
+        <v>1010000896</v>
       </c>
       <c r="B374" s="8" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C374" s="6" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="375" spans="1:3" ht="15.75">
+    <row r="375" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" s="8">
-        <v>1010084035</v>
+        <v>1010084308</v>
       </c>
       <c r="B375" s="8" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C375" s="6" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="376" spans="1:3" ht="15.75">
-      <c r="A376" s="2"/>
-      <c r="B376" s="2"/>
-    </row>
-    <row r="377" spans="1:3" ht="15.75">
+    <row r="376" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A376" s="8">
+        <v>1010084035</v>
+      </c>
+      <c r="B376" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="C376" s="6" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" s="2"/>
       <c r="B377" s="2"/>
     </row>
-    <row r="378" spans="1:3" ht="15.75">
+    <row r="378" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" s="2"/>
       <c r="B378" s="2"/>
     </row>
-    <row r="379" spans="1:3" ht="15.75">
+    <row r="379" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
     </row>
-    <row r="380" spans="1:3" ht="15.75">
+    <row r="380" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
     </row>
-    <row r="381" spans="1:3" ht="15.75">
+    <row r="381" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" s="2"/>
       <c r="B381" s="2"/>
     </row>
-    <row r="382" spans="1:3" ht="15.75">
+    <row r="382" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" s="2"/>
       <c r="B382" s="2"/>
     </row>
-    <row r="383" spans="1:3" ht="15.75">
+    <row r="383" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" s="2"/>
       <c r="B383" s="2"/>
     </row>
-    <row r="384" spans="1:3" ht="15.75">
+    <row r="384" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" s="2"/>
       <c r="B384" s="2"/>
     </row>
-    <row r="385" spans="1:2" ht="15.75">
+    <row r="385" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" s="2"/>
       <c r="B385" s="2"/>
     </row>
-    <row r="386" spans="1:2" ht="15.75">
+    <row r="386" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" s="2"/>
       <c r="B386" s="2"/>
     </row>
-    <row r="387" spans="1:2" ht="15.75">
+    <row r="387" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" s="2"/>
       <c r="B387" s="2"/>
     </row>
-    <row r="388" spans="1:2" ht="15.75">
+    <row r="388" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" s="2"/>
       <c r="B388" s="2"/>
     </row>
-    <row r="389" spans="1:2" ht="15.75">
+    <row r="389" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" s="2"/>
       <c r="B389" s="2"/>
     </row>
-    <row r="390" spans="1:2" ht="15.75">
+    <row r="390" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" s="2"/>
       <c r="B390" s="2"/>
     </row>
-    <row r="391" spans="1:2" ht="15.75">
+    <row r="391" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" s="2"/>
       <c r="B391" s="2"/>
     </row>
-    <row r="392" spans="1:2" ht="15.75">
+    <row r="392" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" s="2"/>
       <c r="B392" s="2"/>
     </row>
-    <row r="393" spans="1:2" ht="15.75">
+    <row r="393" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" s="2"/>
       <c r="B393" s="2"/>
     </row>
-    <row r="394" spans="1:2" ht="15.75">
+    <row r="394" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" s="2"/>
       <c r="B394" s="2"/>
     </row>
-    <row r="395" spans="1:2" ht="15.75">
+    <row r="395" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" s="2"/>
       <c r="B395" s="2"/>
     </row>
-    <row r="396" spans="1:2" ht="15.75">
+    <row r="396" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" s="2"/>
       <c r="B396" s="2"/>
     </row>
-    <row r="397" spans="1:2" ht="15.75">
+    <row r="397" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" s="2"/>
       <c r="B397" s="2"/>
     </row>
-    <row r="398" spans="1:2" ht="15.75">
+    <row r="398" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" s="2"/>
       <c r="B398" s="2"/>
     </row>
-    <row r="399" spans="1:2" ht="15.75">
+    <row r="399" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" s="2"/>
       <c r="B399" s="2"/>
     </row>
-    <row r="400" spans="1:2" ht="15.75">
+    <row r="400" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" s="2"/>
       <c r="B400" s="2"/>
     </row>
-    <row r="401" spans="1:2" ht="15.75">
+    <row r="401" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" s="2"/>
       <c r="B401" s="2"/>
     </row>
-    <row r="402" spans="1:2" ht="15.75">
+    <row r="402" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" s="2"/>
       <c r="B402" s="2"/>
     </row>
-    <row r="403" spans="1:2" ht="15.75">
+    <row r="403" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" s="2"/>
       <c r="B403" s="2"/>
     </row>
-    <row r="404" spans="1:2" ht="15.75">
+    <row r="404" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" s="2"/>
       <c r="B404" s="2"/>
     </row>
-    <row r="405" spans="1:2" ht="15.75">
+    <row r="405" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" s="2"/>
       <c r="B405" s="2"/>
     </row>
-    <row r="406" spans="1:2" ht="15.75">
+    <row r="406" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" s="2"/>
       <c r="B406" s="2"/>
     </row>
-    <row r="407" spans="1:2" ht="15.75">
+    <row r="407" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" s="2"/>
       <c r="B407" s="2"/>
     </row>
-    <row r="408" spans="1:2" ht="15.75">
+    <row r="408" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" s="2"/>
       <c r="B408" s="2"/>
     </row>
-    <row r="409" spans="1:2" ht="15.75">
+    <row r="409" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" s="2"/>
       <c r="B409" s="2"/>
     </row>
-    <row r="410" spans="1:2" ht="15.75">
+    <row r="410" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" s="2"/>
       <c r="B410" s="2"/>
     </row>
-    <row r="411" spans="1:2" ht="15.75">
+    <row r="411" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" s="2"/>
       <c r="B411" s="2"/>
     </row>
-    <row r="412" spans="1:2" ht="15.75">
+    <row r="412" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" s="2"/>
       <c r="B412" s="2"/>
     </row>
-    <row r="413" spans="1:2" ht="15.75">
+    <row r="413" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" s="2"/>
       <c r="B413" s="2"/>
     </row>
-    <row r="414" spans="1:2" ht="15.75">
+    <row r="414" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" s="2"/>
       <c r="B414" s="2"/>
     </row>
-    <row r="415" spans="1:2" ht="15.75">
+    <row r="415" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" s="2"/>
       <c r="B415" s="2"/>
     </row>
-    <row r="416" spans="1:2" ht="15.75">
+    <row r="416" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" s="2"/>
       <c r="B416" s="2"/>
     </row>
-    <row r="417" spans="1:2" ht="15.75">
+    <row r="417" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" s="2"/>
       <c r="B417" s="2"/>
     </row>
-    <row r="418" spans="1:2" ht="15.75">
+    <row r="418" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" s="2"/>
       <c r="B418" s="2"/>
     </row>
-    <row r="419" spans="1:2" ht="15.75">
+    <row r="419" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" s="2"/>
       <c r="B419" s="2"/>
     </row>
-    <row r="420" spans="1:2" ht="15.75">
+    <row r="420" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" s="2"/>
       <c r="B420" s="2"/>
     </row>
-    <row r="421" spans="1:2" ht="15.75">
+    <row r="421" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" s="2"/>
       <c r="B421" s="2"/>
     </row>
-    <row r="422" spans="1:2" ht="15.75">
+    <row r="422" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" s="2"/>
       <c r="B422" s="2"/>
     </row>
-    <row r="423" spans="1:2" ht="15.75">
+    <row r="423" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" s="2"/>
       <c r="B423" s="2"/>
     </row>
-    <row r="424" spans="1:2" ht="15.75">
+    <row r="424" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" s="2"/>
       <c r="B424" s="2"/>
     </row>
-    <row r="425" spans="1:2" ht="15.75">
+    <row r="425" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" s="2"/>
       <c r="B425" s="2"/>
     </row>
-    <row r="426" spans="1:2" ht="15.75">
+    <row r="426" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" s="2"/>
       <c r="B426" s="2"/>
     </row>
-    <row r="427" spans="1:2" ht="15.75">
+    <row r="427" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" s="2"/>
       <c r="B427" s="2"/>
     </row>
-    <row r="428" spans="1:2" ht="15.75">
+    <row r="428" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" s="2"/>
       <c r="B428" s="2"/>
     </row>
-    <row r="429" spans="1:2" ht="15.75">
+    <row r="429" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" s="2"/>
       <c r="B429" s="2"/>
     </row>
-    <row r="430" spans="1:2" ht="15.75">
+    <row r="430" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" s="2"/>
       <c r="B430" s="2"/>
     </row>
-    <row r="431" spans="1:2" ht="15.75">
+    <row r="431" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" s="2"/>
       <c r="B431" s="2"/>
     </row>
-    <row r="432" spans="1:2" ht="15.75">
+    <row r="432" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" s="2"/>
       <c r="B432" s="2"/>
     </row>
-    <row r="433" spans="1:2" ht="15.75">
+    <row r="433" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" s="2"/>
       <c r="B433" s="2"/>
     </row>
-    <row r="434" spans="1:2" ht="15.75">
+    <row r="434" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" s="2"/>
       <c r="B434" s="2"/>
     </row>
-    <row r="435" spans="1:2" ht="15.75">
+    <row r="435" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" s="2"/>
       <c r="B435" s="2"/>
     </row>
-    <row r="436" spans="1:2" ht="15.75">
+    <row r="436" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" s="2"/>
       <c r="B436" s="2"/>
     </row>
-    <row r="437" spans="1:2" ht="15.75">
+    <row r="437" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" s="2"/>
       <c r="B437" s="2"/>
     </row>
-    <row r="438" spans="1:2" ht="15.75">
+    <row r="438" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" s="2"/>
       <c r="B438" s="2"/>
     </row>
-    <row r="439" spans="1:2" ht="15.75">
+    <row r="439" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" s="2"/>
       <c r="B439" s="2"/>
     </row>
-    <row r="440" spans="1:2" ht="15.75">
+    <row r="440" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" s="2"/>
       <c r="B440" s="2"/>
     </row>
-    <row r="441" spans="1:2" ht="15.75">
+    <row r="441" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" s="2"/>
       <c r="B441" s="2"/>
     </row>
-    <row r="442" spans="1:2" ht="15.75">
+    <row r="442" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" s="2"/>
       <c r="B442" s="2"/>
     </row>
-    <row r="443" spans="1:2" ht="15.75">
+    <row r="443" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" s="2"/>
       <c r="B443" s="2"/>
     </row>
-    <row r="444" spans="1:2" ht="15.75">
+    <row r="444" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" s="2"/>
       <c r="B444" s="2"/>
     </row>
-    <row r="445" spans="1:2" ht="15.75">
+    <row r="445" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" s="2"/>
       <c r="B445" s="2"/>
     </row>
-    <row r="446" spans="1:2" ht="15.75">
+    <row r="446" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" s="2"/>
       <c r="B446" s="2"/>
     </row>
-    <row r="447" spans="1:2" ht="15.75">
+    <row r="447" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" s="2"/>
       <c r="B447" s="2"/>
     </row>
-    <row r="448" spans="1:2" ht="15.75">
+    <row r="448" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" s="2"/>
       <c r="B448" s="2"/>
     </row>
-    <row r="449" spans="1:2" ht="15.75">
+    <row r="449" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" s="2"/>
       <c r="B449" s="2"/>
     </row>
-    <row r="450" spans="1:2" ht="15.75">
+    <row r="450" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" s="2"/>
       <c r="B450" s="2"/>
     </row>
-    <row r="451" spans="1:2" ht="15.75">
+    <row r="451" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" s="2"/>
       <c r="B451" s="2"/>
     </row>
-    <row r="452" spans="1:2" ht="15.75">
+    <row r="452" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" s="2"/>
       <c r="B452" s="2"/>
     </row>
-    <row r="453" spans="1:2" ht="15.75">
+    <row r="453" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" s="2"/>
       <c r="B453" s="2"/>
     </row>
-    <row r="454" spans="1:2" ht="15.75">
+    <row r="454" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" s="2"/>
       <c r="B454" s="2"/>
     </row>
-    <row r="455" spans="1:2" ht="15.75">
+    <row r="455" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" s="2"/>
       <c r="B455" s="2"/>
     </row>
-    <row r="456" spans="1:2" ht="15.75">
+    <row r="456" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" s="2"/>
       <c r="B456" s="2"/>
     </row>
-    <row r="457" spans="1:2" ht="15.75">
+    <row r="457" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" s="2"/>
       <c r="B457" s="2"/>
     </row>
-    <row r="458" spans="1:2" ht="15.75">
+    <row r="458" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" s="2"/>
       <c r="B458" s="2"/>
     </row>
-    <row r="459" spans="1:2" ht="15.75">
+    <row r="459" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" s="2"/>
       <c r="B459" s="2"/>
     </row>
-    <row r="460" spans="1:2" ht="15.75">
+    <row r="460" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" s="2"/>
       <c r="B460" s="2"/>
     </row>
-    <row r="461" spans="1:2" ht="15.75">
+    <row r="461" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" s="2"/>
       <c r="B461" s="2"/>
     </row>
-    <row r="462" spans="1:2" ht="15.75">
+    <row r="462" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" s="2"/>
       <c r="B462" s="2"/>
     </row>
-    <row r="463" spans="1:2" ht="15.75">
+    <row r="463" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" s="2"/>
       <c r="B463" s="2"/>
     </row>
-    <row r="464" spans="1:2" ht="15.75">
+    <row r="464" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" s="2"/>
       <c r="B464" s="2"/>
     </row>
-    <row r="465" spans="1:2" ht="15.75">
+    <row r="465" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" s="2"/>
       <c r="B465" s="2"/>
     </row>
-    <row r="466" spans="1:2" ht="15.75">
+    <row r="466" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" s="2"/>
       <c r="B466" s="2"/>
     </row>
-    <row r="467" spans="1:2" ht="15.75">
+    <row r="467" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" s="2"/>
       <c r="B467" s="2"/>
     </row>
-    <row r="468" spans="1:2" ht="15.75">
+    <row r="468" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" s="2"/>
       <c r="B468" s="2"/>
     </row>
-    <row r="469" spans="1:2" ht="15.75">
+    <row r="469" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" s="2"/>
       <c r="B469" s="2"/>
     </row>
-    <row r="470" spans="1:2" ht="15.75">
+    <row r="470" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" s="2"/>
       <c r="B470" s="2"/>
     </row>
-    <row r="471" spans="1:2" ht="15.75">
+    <row r="471" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" s="2"/>
       <c r="B471" s="2"/>
     </row>
-    <row r="472" spans="1:2" ht="15.75">
+    <row r="472" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" s="2"/>
       <c r="B472" s="2"/>
     </row>
-    <row r="473" spans="1:2" ht="15.75">
+    <row r="473" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" s="2"/>
       <c r="B473" s="2"/>
     </row>
-    <row r="474" spans="1:2" ht="15.75">
+    <row r="474" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" s="2"/>
       <c r="B474" s="2"/>
     </row>
-    <row r="475" spans="1:2" ht="15.75">
+    <row r="475" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" s="2"/>
       <c r="B475" s="2"/>
     </row>
-    <row r="476" spans="1:2" ht="15.75">
+    <row r="476" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" s="2"/>
       <c r="B476" s="2"/>
     </row>
-    <row r="477" spans="1:2" ht="15.75">
+    <row r="477" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" s="2"/>
       <c r="B477" s="2"/>
     </row>
-    <row r="478" spans="1:2" ht="15.75">
+    <row r="478" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A478" s="2"/>
       <c r="B478" s="2"/>
     </row>
-    <row r="479" spans="1:2" ht="15.75">
+    <row r="479" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" s="2"/>
       <c r="B479" s="2"/>
     </row>
-    <row r="480" spans="1:2" ht="15.75">
+    <row r="480" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A480" s="2"/>
       <c r="B480" s="2"/>
     </row>
-    <row r="481" spans="1:2" ht="15.75">
+    <row r="481" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" s="2"/>
       <c r="B481" s="2"/>
     </row>
-    <row r="482" spans="1:2" ht="15.75">
+    <row r="482" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" s="2"/>
       <c r="B482" s="2"/>
     </row>
-    <row r="483" spans="1:2" ht="15.75">
+    <row r="483" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" s="2"/>
       <c r="B483" s="2"/>
     </row>
-    <row r="484" spans="1:2" ht="15.75">
+    <row r="484" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" s="2"/>
       <c r="B484" s="2"/>
     </row>
-    <row r="485" spans="1:2" ht="15.75">
+    <row r="485" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" s="2"/>
       <c r="B485" s="2"/>
     </row>
-    <row r="486" spans="1:2" ht="15.75">
+    <row r="486" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" s="2"/>
       <c r="B486" s="2"/>
     </row>
-    <row r="487" spans="1:2" ht="15.75">
+    <row r="487" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" s="2"/>
       <c r="B487" s="2"/>
     </row>
-    <row r="488" spans="1:2" ht="15.75">
+    <row r="488" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" s="2"/>
       <c r="B488" s="2"/>
     </row>
-    <row r="489" spans="1:2" ht="15.75">
+    <row r="489" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" s="2"/>
       <c r="B489" s="2"/>
     </row>
-    <row r="490" spans="1:2" ht="15.75">
+    <row r="490" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" s="2"/>
       <c r="B490" s="2"/>
     </row>
-    <row r="491" spans="1:2" ht="15.75">
+    <row r="491" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" s="2"/>
       <c r="B491" s="2"/>
     </row>
-    <row r="492" spans="1:2" ht="15.75">
+    <row r="492" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" s="2"/>
       <c r="B492" s="2"/>
     </row>
-    <row r="493" spans="1:2" ht="15.75">
+    <row r="493" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" s="2"/>
       <c r="B493" s="2"/>
     </row>
-    <row r="494" spans="1:2" ht="15.75">
+    <row r="494" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" s="2"/>
       <c r="B494" s="2"/>
     </row>
-    <row r="495" spans="1:2" ht="15.75">
+    <row r="495" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" s="2"/>
       <c r="B495" s="2"/>
     </row>
-    <row r="496" spans="1:2" ht="15.75">
+    <row r="496" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" s="2"/>
       <c r="B496" s="2"/>
     </row>
-    <row r="497" spans="1:2" ht="15.75">
+    <row r="497" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A497" s="2"/>
       <c r="B497" s="2"/>
     </row>
-    <row r="498" spans="1:2" ht="15.75">
+    <row r="498" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A498" s="2"/>
       <c r="B498" s="2"/>
     </row>
-    <row r="499" spans="1:2" ht="15.75">
+    <row r="499" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" s="2"/>
       <c r="B499" s="2"/>
     </row>
-    <row r="500" spans="1:2" ht="15.75">
+    <row r="500" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" s="2"/>
       <c r="B500" s="2"/>
     </row>
-    <row r="501" spans="1:2" ht="15.75">
+    <row r="501" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" s="2"/>
       <c r="B501" s="2"/>
     </row>
-    <row r="502" spans="1:2" ht="15.75">
+    <row r="502" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" s="2"/>
       <c r="B502" s="2"/>
     </row>
-    <row r="503" spans="1:2" ht="15.75">
+    <row r="503" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A503" s="2"/>
       <c r="B503" s="2"/>
     </row>
-    <row r="504" spans="1:2" ht="15.75">
+    <row r="504" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A504" s="2"/>
       <c r="B504" s="2"/>
     </row>
-    <row r="505" spans="1:2" ht="15.75">
+    <row r="505" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A505" s="2"/>
       <c r="B505" s="2"/>
     </row>
-    <row r="506" spans="1:2" ht="15.75">
+    <row r="506" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A506" s="2"/>
       <c r="B506" s="2"/>
     </row>
-    <row r="507" spans="1:2" ht="15.75">
+    <row r="507" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A507" s="2"/>
       <c r="B507" s="2"/>
     </row>
-    <row r="508" spans="1:2" ht="15.75">
+    <row r="508" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" s="2"/>
       <c r="B508" s="2"/>
     </row>
-    <row r="509" spans="1:2" ht="15.75">
+    <row r="509" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A509" s="2"/>
       <c r="B509" s="2"/>
     </row>
-    <row r="510" spans="1:2" ht="15.75">
+    <row r="510" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A510" s="2"/>
       <c r="B510" s="2"/>
     </row>
-    <row r="511" spans="1:2" ht="15.75">
+    <row r="511" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" s="2"/>
       <c r="B511" s="2"/>
     </row>
-    <row r="512" spans="1:2" ht="15.75">
+    <row r="512" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A512" s="2"/>
       <c r="B512" s="2"/>
     </row>
-    <row r="513" spans="1:2" ht="15.75">
+    <row r="513" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A513" s="2"/>
       <c r="B513" s="2"/>
     </row>
-    <row r="514" spans="1:2" ht="15.75">
+    <row r="514" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A514" s="2"/>
       <c r="B514" s="2"/>
     </row>
-    <row r="515" spans="1:2" ht="15.75">
+    <row r="515" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A515" s="2"/>
       <c r="B515" s="2"/>
     </row>
-    <row r="516" spans="1:2" ht="15.75">
+    <row r="516" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A516" s="2"/>
       <c r="B516" s="2"/>
     </row>
-    <row r="517" spans="1:2" ht="15.75">
+    <row r="517" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A517" s="2"/>
       <c r="B517" s="2"/>
     </row>
-    <row r="518" spans="1:2" ht="15.75">
+    <row r="518" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A518" s="2"/>
       <c r="B518" s="2"/>
     </row>
-    <row r="519" spans="1:2" ht="15.75">
+    <row r="519" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A519" s="2"/>
       <c r="B519" s="2"/>
     </row>
-    <row r="520" spans="1:2" ht="15.75">
+    <row r="520" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A520" s="2"/>
       <c r="B520" s="2"/>
     </row>
-    <row r="521" spans="1:2" ht="15.75">
+    <row r="521" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A521" s="2"/>
       <c r="B521" s="2"/>
     </row>
-    <row r="522" spans="1:2" ht="15.75">
+    <row r="522" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A522" s="2"/>
       <c r="B522" s="2"/>
     </row>
-    <row r="523" spans="1:2" ht="15.75">
+    <row r="523" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A523" s="2"/>
       <c r="B523" s="2"/>
     </row>
-    <row r="524" spans="1:2" ht="15.75">
+    <row r="524" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A524" s="2"/>
       <c r="B524" s="2"/>
     </row>
-    <row r="525" spans="1:2" ht="15.75">
+    <row r="525" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A525" s="2"/>
       <c r="B525" s="2"/>
     </row>
-    <row r="526" spans="1:2" ht="15.75">
+    <row r="526" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A526" s="2"/>
       <c r="B526" s="2"/>
     </row>
-    <row r="527" spans="1:2" ht="15.75">
+    <row r="527" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A527" s="2"/>
       <c r="B527" s="2"/>
     </row>
-    <row r="528" spans="1:2" ht="15.75">
+    <row r="528" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A528" s="2"/>
       <c r="B528" s="2"/>
     </row>
-    <row r="529" spans="1:2" ht="15.75">
+    <row r="529" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A529" s="2"/>
       <c r="B529" s="2"/>
     </row>
-    <row r="530" spans="1:2" ht="15.75">
+    <row r="530" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A530" s="2"/>
       <c r="B530" s="2"/>
     </row>
-    <row r="531" spans="1:2" ht="15.75">
+    <row r="531" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A531" s="2"/>
       <c r="B531" s="2"/>
     </row>
-    <row r="532" spans="1:2" ht="15.75">
+    <row r="532" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A532" s="2"/>
       <c r="B532" s="2"/>
     </row>
-    <row r="533" spans="1:2" ht="15.75">
+    <row r="533" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A533" s="2"/>
       <c r="B533" s="2"/>
     </row>
-    <row r="534" spans="1:2" ht="15.75">
+    <row r="534" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A534" s="2"/>
       <c r="B534" s="2"/>
     </row>
-    <row r="535" spans="1:2" ht="15.75">
+    <row r="535" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A535" s="2"/>
       <c r="B535" s="2"/>
     </row>
-    <row r="536" spans="1:2" ht="15.75">
+    <row r="536" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A536" s="2"/>
       <c r="B536" s="2"/>
     </row>
-    <row r="537" spans="1:2" ht="15.75">
+    <row r="537" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A537" s="2"/>
       <c r="B537" s="2"/>
     </row>
-    <row r="538" spans="1:2" ht="15.75">
+    <row r="538" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A538" s="2"/>
       <c r="B538" s="2"/>
     </row>
-    <row r="539" spans="1:2" ht="15.75">
+    <row r="539" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A539" s="2"/>
       <c r="B539" s="2"/>
     </row>
-    <row r="540" spans="1:2" ht="15.75">
+    <row r="540" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A540" s="2"/>
       <c r="B540" s="2"/>
     </row>
-    <row r="541" spans="1:2" ht="15.75">
+    <row r="541" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A541" s="2"/>
       <c r="B541" s="2"/>
     </row>
-    <row r="542" spans="1:2" ht="15.75">
+    <row r="542" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A542" s="2"/>
       <c r="B542" s="2"/>
     </row>
-    <row r="543" spans="1:2" ht="15.75">
+    <row r="543" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A543" s="2"/>
       <c r="B543" s="2"/>
     </row>
-    <row r="544" spans="1:2" ht="15.75">
+    <row r="544" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A544" s="2"/>
       <c r="B544" s="2"/>
     </row>
-    <row r="545" spans="1:2" ht="15.75">
+    <row r="545" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A545" s="2"/>
       <c r="B545" s="2"/>
     </row>
-    <row r="546" spans="1:2" ht="15.75">
+    <row r="546" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A546" s="2"/>
       <c r="B546" s="2"/>
     </row>
-    <row r="547" spans="1:2" ht="15.75">
+    <row r="547" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A547" s="2"/>
       <c r="B547" s="2"/>
     </row>
-    <row r="548" spans="1:2" ht="15.75">
+    <row r="548" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A548" s="2"/>
       <c r="B548" s="2"/>
     </row>
-    <row r="549" spans="1:2" ht="15.75">
+    <row r="549" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A549" s="2"/>
       <c r="B549" s="2"/>
     </row>
-    <row r="550" spans="1:2" ht="15.75">
+    <row r="550" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A550" s="2"/>
       <c r="B550" s="2"/>
     </row>
-    <row r="551" spans="1:2" ht="15.75">
+    <row r="551" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A551" s="2"/>
       <c r="B551" s="2"/>
     </row>
-    <row r="552" spans="1:2" ht="15.75">
+    <row r="552" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A552" s="2"/>
       <c r="B552" s="2"/>
     </row>
-    <row r="553" spans="1:2" ht="15.75">
+    <row r="553" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A553" s="2"/>
       <c r="B553" s="2"/>
     </row>
-    <row r="554" spans="1:2" ht="15.75">
+    <row r="554" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A554" s="2"/>
       <c r="B554" s="2"/>
     </row>
-    <row r="555" spans="1:2" ht="15.75">
+    <row r="555" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A555" s="2"/>
       <c r="B555" s="2"/>
     </row>
-    <row r="556" spans="1:2" ht="15.75">
+    <row r="556" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A556" s="2"/>
       <c r="B556" s="2"/>
     </row>
-    <row r="557" spans="1:2" ht="15.75">
+    <row r="557" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A557" s="2"/>
       <c r="B557" s="2"/>
     </row>
-    <row r="558" spans="1:2" ht="15.75">
+    <row r="558" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A558" s="2"/>
       <c r="B558" s="2"/>
     </row>
-    <row r="559" spans="1:2" ht="15.75">
+    <row r="559" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A559" s="2"/>
       <c r="B559" s="2"/>
     </row>
-    <row r="560" spans="1:2" ht="15.75">
+    <row r="560" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A560" s="2"/>
       <c r="B560" s="2"/>
     </row>
-    <row r="561" spans="1:2" ht="15.75">
+    <row r="561" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A561" s="2"/>
       <c r="B561" s="2"/>
     </row>
-    <row r="562" spans="1:2" ht="15.75">
+    <row r="562" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A562" s="2"/>
       <c r="B562" s="2"/>
     </row>
-    <row r="563" spans="1:2" ht="15.75">
+    <row r="563" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A563" s="2"/>
       <c r="B563" s="2"/>
     </row>
-    <row r="564" spans="1:2" ht="15.75">
+    <row r="564" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A564" s="2"/>
       <c r="B564" s="2"/>
     </row>
-    <row r="565" spans="1:2" ht="15.75">
+    <row r="565" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A565" s="2"/>
       <c r="B565" s="2"/>
     </row>
-    <row r="566" spans="1:2" ht="15.75">
+    <row r="566" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A566" s="2"/>
       <c r="B566" s="2"/>
     </row>
-    <row r="567" spans="1:2" ht="15.75">
+    <row r="567" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A567" s="2"/>
       <c r="B567" s="2"/>
     </row>
-    <row r="568" spans="1:2" ht="15.75">
+    <row r="568" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A568" s="2"/>
       <c r="B568" s="2"/>
     </row>
-    <row r="569" spans="1:2" ht="15.75">
+    <row r="569" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A569" s="2"/>
       <c r="B569" s="2"/>
     </row>
-    <row r="570" spans="1:2" ht="15.75">
+    <row r="570" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A570" s="2"/>
       <c r="B570" s="2"/>
     </row>
-    <row r="571" spans="1:2" ht="15.75">
+    <row r="571" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A571" s="2"/>
       <c r="B571" s="2"/>
     </row>
-    <row r="572" spans="1:2" ht="15.75">
+    <row r="572" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A572" s="2"/>
       <c r="B572" s="2"/>
     </row>
-    <row r="573" spans="1:2" ht="15.75">
+    <row r="573" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A573" s="2"/>
       <c r="B573" s="2"/>
     </row>
-    <row r="574" spans="1:2" ht="15.75">
+    <row r="574" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A574" s="2"/>
       <c r="B574" s="2"/>
     </row>
-    <row r="575" spans="1:2" ht="15.75">
+    <row r="575" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A575" s="2"/>
       <c r="B575" s="2"/>
     </row>
-    <row r="576" spans="1:2" ht="15.75">
+    <row r="576" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A576" s="2"/>
       <c r="B576" s="2"/>
     </row>
-    <row r="577" spans="1:2" ht="15.75">
+    <row r="577" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A577" s="2"/>
       <c r="B577" s="2"/>
     </row>
-    <row r="578" spans="1:2" ht="15.75">
+    <row r="578" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A578" s="2"/>
       <c r="B578" s="2"/>
     </row>
-    <row r="579" spans="1:2" ht="15.75">
+    <row r="579" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A579" s="2"/>
       <c r="B579" s="2"/>
     </row>
-    <row r="580" spans="1:2" ht="15.75">
+    <row r="580" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A580" s="2"/>
       <c r="B580" s="2"/>
     </row>
-    <row r="581" spans="1:2" ht="15.75">
+    <row r="581" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A581" s="2"/>
       <c r="B581" s="2"/>
     </row>
-    <row r="582" spans="1:2" ht="15.75">
+    <row r="582" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A582" s="2"/>
       <c r="B582" s="2"/>
     </row>
-    <row r="583" spans="1:2" ht="15.75">
+    <row r="583" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A583" s="2"/>
       <c r="B583" s="2"/>
     </row>
-    <row r="584" spans="1:2" ht="15.75">
+    <row r="584" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A584" s="2"/>
       <c r="B584" s="2"/>
     </row>
-    <row r="585" spans="1:2" ht="15.75">
+    <row r="585" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A585" s="2"/>
       <c r="B585" s="2"/>
     </row>
-    <row r="586" spans="1:2" ht="15.75">
+    <row r="586" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A586" s="2"/>
       <c r="B586" s="2"/>
     </row>
-    <row r="587" spans="1:2" ht="15.75">
+    <row r="587" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A587" s="2"/>
       <c r="B587" s="2"/>
     </row>
-    <row r="588" spans="1:2" ht="15.75">
+    <row r="588" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A588" s="2"/>
       <c r="B588" s="2"/>
     </row>
-    <row r="589" spans="1:2" ht="15.75">
+    <row r="589" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A589" s="2"/>
       <c r="B589" s="2"/>
     </row>
-    <row r="590" spans="1:2" ht="15.75">
+    <row r="590" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A590" s="2"/>
       <c r="B590" s="2"/>
     </row>
-    <row r="591" spans="1:2" ht="15.75">
+    <row r="591" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A591" s="2"/>
       <c r="B591" s="2"/>
     </row>
-    <row r="592" spans="1:2" ht="15.75">
+    <row r="592" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A592" s="2"/>
       <c r="B592" s="2"/>
     </row>
-    <row r="593" spans="1:2" ht="15.75">
+    <row r="593" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A593" s="2"/>
       <c r="B593" s="2"/>
     </row>
-    <row r="594" spans="1:2" ht="15.75">
+    <row r="594" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A594" s="2"/>
       <c r="B594" s="2"/>
     </row>
-    <row r="595" spans="1:2" ht="15.75">
+    <row r="595" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A595" s="2"/>
       <c r="B595" s="2"/>
     </row>
-    <row r="596" spans="1:2" ht="15.75">
+    <row r="596" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A596" s="2"/>
       <c r="B596" s="2"/>
     </row>
-    <row r="597" spans="1:2" ht="15.75">
+    <row r="597" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A597" s="2"/>
       <c r="B597" s="2"/>
     </row>
-    <row r="598" spans="1:2" ht="15.75">
+    <row r="598" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A598" s="2"/>
       <c r="B598" s="2"/>
     </row>
-    <row r="599" spans="1:2" ht="15.75">
+    <row r="599" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A599" s="2"/>
       <c r="B599" s="2"/>
     </row>
-    <row r="600" spans="1:2" ht="15.75">
+    <row r="600" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A600" s="2"/>
       <c r="B600" s="2"/>
     </row>
-    <row r="601" spans="1:2" ht="15.75">
+    <row r="601" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A601" s="2"/>
       <c r="B601" s="2"/>
     </row>
-    <row r="602" spans="1:2" ht="15.75">
+    <row r="602" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A602" s="2"/>
       <c r="B602" s="2"/>
     </row>
-    <row r="603" spans="1:2" ht="15.75">
+    <row r="603" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A603" s="2"/>
       <c r="B603" s="2"/>
     </row>
-    <row r="604" spans="1:2" ht="15.75">
+    <row r="604" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A604" s="2"/>
       <c r="B604" s="2"/>
     </row>
-    <row r="605" spans="1:2" ht="15.75">
+    <row r="605" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A605" s="2"/>
       <c r="B605" s="2"/>
     </row>
-    <row r="606" spans="1:2" ht="15.75">
+    <row r="606" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A606" s="2"/>
       <c r="B606" s="2"/>
     </row>
-    <row r="607" spans="1:2" ht="15.75">
+    <row r="607" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A607" s="2"/>
       <c r="B607" s="2"/>
     </row>
-    <row r="608" spans="1:2" ht="15.75">
+    <row r="608" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A608" s="2"/>
       <c r="B608" s="2"/>
     </row>
-    <row r="609" spans="1:2" ht="15.75">
+    <row r="609" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A609" s="2"/>
       <c r="B609" s="2"/>
     </row>
-    <row r="610" spans="1:2" ht="15.75">
+    <row r="610" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A610" s="2"/>
       <c r="B610" s="2"/>
     </row>
-    <row r="611" spans="1:2" ht="15.75">
+    <row r="611" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A611" s="2"/>
       <c r="B611" s="2"/>
     </row>
-    <row r="612" spans="1:2" ht="15.75">
+    <row r="612" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A612" s="2"/>
       <c r="B612" s="2"/>
     </row>
-    <row r="613" spans="1:2" ht="15.75">
+    <row r="613" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A613" s="2"/>
       <c r="B613" s="2"/>
     </row>
-    <row r="614" spans="1:2" ht="15.75">
+    <row r="614" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A614" s="2"/>
       <c r="B614" s="2"/>
     </row>
-    <row r="615" spans="1:2" ht="15.75">
+    <row r="615" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A615" s="2"/>
       <c r="B615" s="2"/>
     </row>
-    <row r="616" spans="1:2" ht="15.75">
+    <row r="616" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A616" s="2"/>
       <c r="B616" s="2"/>
     </row>
-    <row r="617" spans="1:2" ht="15.75">
+    <row r="617" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A617" s="2"/>
       <c r="B617" s="2"/>
     </row>
-    <row r="618" spans="1:2" ht="15.75">
+    <row r="618" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A618" s="2"/>
       <c r="B618" s="2"/>
     </row>
-    <row r="619" spans="1:2" ht="15.75">
+    <row r="619" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A619" s="2"/>
       <c r="B619" s="2"/>
     </row>
-    <row r="620" spans="1:2" ht="15.75">
+    <row r="620" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A620" s="2"/>
       <c r="B620" s="2"/>
     </row>
-    <row r="621" spans="1:2" ht="15.75">
+    <row r="621" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A621" s="2"/>
       <c r="B621" s="2"/>
     </row>
-    <row r="622" spans="1:2" ht="15.75">
+    <row r="622" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A622" s="2"/>
       <c r="B622" s="2"/>
     </row>
-    <row r="623" spans="1:2" ht="15.75">
+    <row r="623" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A623" s="2"/>
       <c r="B623" s="2"/>
     </row>
-    <row r="624" spans="1:2" ht="15.75">
+    <row r="624" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A624" s="2"/>
       <c r="B624" s="2"/>
     </row>
-    <row r="625" spans="1:2" ht="15.75">
+    <row r="625" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A625" s="2"/>
       <c r="B625" s="2"/>
     </row>
-    <row r="626" spans="1:2" ht="15.75">
+    <row r="626" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A626" s="2"/>
       <c r="B626" s="2"/>
     </row>
-    <row r="627" spans="1:2" ht="15.75">
+    <row r="627" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A627" s="2"/>
       <c r="B627" s="2"/>
     </row>
-    <row r="628" spans="1:2" ht="15.75">
+    <row r="628" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A628" s="2"/>
       <c r="B628" s="2"/>
     </row>
-    <row r="629" spans="1:2" ht="15.75">
+    <row r="629" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A629" s="2"/>
       <c r="B629" s="2"/>
     </row>
-    <row r="630" spans="1:2" ht="15.75">
+    <row r="630" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A630" s="2"/>
       <c r="B630" s="2"/>
     </row>
-    <row r="631" spans="1:2" ht="15.75">
+    <row r="631" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A631" s="2"/>
       <c r="B631" s="2"/>
     </row>
-    <row r="632" spans="1:2" ht="15.75">
+    <row r="632" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A632" s="2"/>
       <c r="B632" s="2"/>
     </row>
-    <row r="633" spans="1:2" ht="15.75">
+    <row r="633" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A633" s="2"/>
       <c r="B633" s="2"/>
     </row>
-    <row r="634" spans="1:2" ht="15.75">
+    <row r="634" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A634" s="2"/>
       <c r="B634" s="2"/>
     </row>
-    <row r="635" spans="1:2" ht="15.75">
+    <row r="635" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A635" s="2"/>
       <c r="B635" s="2"/>
     </row>
-    <row r="636" spans="1:2" ht="15.75">
+    <row r="636" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A636" s="2"/>
       <c r="B636" s="2"/>
     </row>
-    <row r="637" spans="1:2" ht="15.75">
+    <row r="637" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A637" s="2"/>
       <c r="B637" s="2"/>
     </row>
-    <row r="638" spans="1:2" ht="15.75">
+    <row r="638" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A638" s="2"/>
       <c r="B638" s="2"/>
     </row>
-    <row r="639" spans="1:2" ht="15.75">
+    <row r="639" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A639" s="2"/>
       <c r="B639" s="2"/>
     </row>
-    <row r="640" spans="1:2" ht="15.75">
+    <row r="640" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A640" s="2"/>
       <c r="B640" s="2"/>
     </row>
-    <row r="641" spans="1:2" ht="15.75">
+    <row r="641" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A641" s="2"/>
       <c r="B641" s="2"/>
     </row>
-    <row r="642" spans="1:2" ht="15.75">
+    <row r="642" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A642" s="2"/>
       <c r="B642" s="2"/>
     </row>
-    <row r="643" spans="1:2" ht="15.75">
+    <row r="643" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A643" s="2"/>
       <c r="B643" s="2"/>
     </row>
-    <row r="644" spans="1:2" ht="15.75">
+    <row r="644" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A644" s="2"/>
       <c r="B644" s="2"/>
     </row>
-    <row r="645" spans="1:2" ht="15.75">
+    <row r="645" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A645" s="2"/>
       <c r="B645" s="2"/>
     </row>
-    <row r="646" spans="1:2" ht="15.75">
+    <row r="646" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A646" s="2"/>
       <c r="B646" s="2"/>
     </row>
-    <row r="647" spans="1:2" ht="15.75">
+    <row r="647" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A647" s="2"/>
       <c r="B647" s="2"/>
     </row>
-    <row r="648" spans="1:2" ht="15.75">
+    <row r="648" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A648" s="2"/>
       <c r="B648" s="2"/>
     </row>
-    <row r="649" spans="1:2" ht="15.75">
+    <row r="649" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A649" s="2"/>
       <c r="B649" s="2"/>
     </row>
-    <row r="650" spans="1:2" ht="15.75">
+    <row r="650" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A650" s="2"/>
       <c r="B650" s="2"/>
     </row>
-    <row r="651" spans="1:2" ht="15.75">
+    <row r="651" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A651" s="2"/>
       <c r="B651" s="2"/>
     </row>
-    <row r="652" spans="1:2" ht="15.75">
+    <row r="652" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A652" s="2"/>
       <c r="B652" s="2"/>
     </row>
-    <row r="653" spans="1:2" ht="15.75">
+    <row r="653" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A653" s="2"/>
       <c r="B653" s="2"/>
     </row>
-    <row r="654" spans="1:2" ht="15.75">
+    <row r="654" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A654" s="2"/>
       <c r="B654" s="2"/>
     </row>
-    <row r="655" spans="1:2" ht="15.75">
+    <row r="655" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A655" s="2"/>
       <c r="B655" s="2"/>
     </row>
-    <row r="656" spans="1:2" ht="15.75">
+    <row r="656" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A656" s="2"/>
       <c r="B656" s="2"/>
     </row>
-    <row r="657" spans="1:2" ht="15.75">
+    <row r="657" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A657" s="2"/>
       <c r="B657" s="2"/>
     </row>
-    <row r="658" spans="1:2" ht="15.75">
+    <row r="658" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A658" s="2"/>
       <c r="B658" s="2"/>
     </row>
-    <row r="659" spans="1:2" ht="15.75">
+    <row r="659" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A659" s="2"/>
       <c r="B659" s="2"/>
     </row>
-    <row r="660" spans="1:2" ht="15.75">
+    <row r="660" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A660" s="2"/>
       <c r="B660" s="2"/>
     </row>
-    <row r="661" spans="1:2" ht="15.75">
+    <row r="661" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A661" s="2"/>
       <c r="B661" s="2"/>
     </row>
-    <row r="662" spans="1:2" ht="15.75">
+    <row r="662" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A662" s="2"/>
       <c r="B662" s="2"/>
     </row>
-    <row r="663" spans="1:2" ht="15.75">
+    <row r="663" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A663" s="2"/>
       <c r="B663" s="2"/>
     </row>
-    <row r="664" spans="1:2" ht="15.75">
+    <row r="664" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A664" s="2"/>
       <c r="B664" s="2"/>
     </row>
-    <row r="665" spans="1:2" ht="15.75">
+    <row r="665" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A665" s="2"/>
       <c r="B665" s="2"/>
     </row>
-    <row r="666" spans="1:2" ht="15.75">
+    <row r="666" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A666" s="2"/>
       <c r="B666" s="2"/>
     </row>
-    <row r="667" spans="1:2" ht="15.75">
+    <row r="667" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A667" s="2"/>
       <c r="B667" s="2"/>
     </row>
-    <row r="668" spans="1:2" ht="15.75">
+    <row r="668" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A668" s="2"/>
       <c r="B668" s="2"/>
     </row>
-    <row r="669" spans="1:2" ht="15.75">
+    <row r="669" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A669" s="2"/>
       <c r="B669" s="2"/>
     </row>
-    <row r="670" spans="1:2" ht="15.75">
+    <row r="670" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A670" s="2"/>
       <c r="B670" s="2"/>
     </row>
-    <row r="671" spans="1:2" ht="15.75">
+    <row r="671" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A671" s="2"/>
       <c r="B671" s="2"/>
     </row>
-    <row r="672" spans="1:2" ht="15.75">
+    <row r="672" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A672" s="2"/>
       <c r="B672" s="2"/>
     </row>
-    <row r="673" spans="1:2" ht="15.75">
+    <row r="673" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A673" s="2"/>
       <c r="B673" s="2"/>
     </row>
-    <row r="674" spans="1:2" ht="15.75">
+    <row r="674" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A674" s="2"/>
       <c r="B674" s="2"/>
     </row>
-    <row r="675" spans="1:2" ht="15.75">
+    <row r="675" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A675" s="2"/>
       <c r="B675" s="2"/>
     </row>
-    <row r="676" spans="1:2" ht="15.75">
+    <row r="676" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A676" s="2"/>
       <c r="B676" s="2"/>
     </row>
-    <row r="677" spans="1:2" ht="15.75">
+    <row r="677" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A677" s="2"/>
       <c r="B677" s="2"/>
     </row>
-    <row r="678" spans="1:2" ht="15.75">
+    <row r="678" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A678" s="2"/>
       <c r="B678" s="2"/>
     </row>
-    <row r="679" spans="1:2" ht="15.75">
+    <row r="679" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A679" s="2"/>
       <c r="B679" s="2"/>
     </row>
-    <row r="680" spans="1:2" ht="15.75">
+    <row r="680" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A680" s="2"/>
       <c r="B680" s="2"/>
     </row>
-    <row r="681" spans="1:2" ht="15.75">
+    <row r="681" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A681" s="2"/>
       <c r="B681" s="2"/>
     </row>
-    <row r="682" spans="1:2" ht="15.75">
+    <row r="682" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A682" s="2"/>
       <c r="B682" s="2"/>
     </row>
-    <row r="683" spans="1:2" ht="15.75">
+    <row r="683" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A683" s="2"/>
       <c r="B683" s="2"/>
     </row>
-    <row r="684" spans="1:2" ht="15.75">
+    <row r="684" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A684" s="2"/>
       <c r="B684" s="2"/>
     </row>
-    <row r="685" spans="1:2" ht="15.75">
+    <row r="685" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A685" s="2"/>
       <c r="B685" s="2"/>
     </row>
-    <row r="686" spans="1:2" ht="15.75">
+    <row r="686" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A686" s="2"/>
       <c r="B686" s="2"/>
     </row>
-    <row r="687" spans="1:2" ht="15.75">
+    <row r="687" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A687" s="2"/>
       <c r="B687" s="2"/>
     </row>
-    <row r="688" spans="1:2" ht="15.75">
+    <row r="688" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A688" s="2"/>
       <c r="B688" s="2"/>
     </row>
-    <row r="689" spans="1:2" ht="15.75">
+    <row r="689" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A689" s="2"/>
       <c r="B689" s="2"/>
     </row>
-    <row r="690" spans="1:2" ht="15.75">
+    <row r="690" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A690" s="2"/>
       <c r="B690" s="2"/>
     </row>
-    <row r="691" spans="1:2" ht="15.75">
+    <row r="691" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A691" s="2"/>
       <c r="B691" s="2"/>
     </row>
-    <row r="692" spans="1:2" ht="15.75">
+    <row r="692" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A692" s="2"/>
       <c r="B692" s="2"/>
     </row>
-    <row r="693" spans="1:2" ht="15.75">
+    <row r="693" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A693" s="2"/>
       <c r="B693" s="2"/>
     </row>
-    <row r="694" spans="1:2" ht="15.75">
+    <row r="694" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A694" s="2"/>
       <c r="B694" s="2"/>
     </row>
-    <row r="695" spans="1:2" ht="15.75">
+    <row r="695" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A695" s="2"/>
       <c r="B695" s="2"/>
     </row>
-    <row r="696" spans="1:2" ht="15.75">
+    <row r="696" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A696" s="2"/>
       <c r="B696" s="2"/>
     </row>
-    <row r="697" spans="1:2" ht="15.75">
+    <row r="697" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A697" s="2"/>
       <c r="B697" s="2"/>
     </row>
-    <row r="698" spans="1:2" ht="15.75">
+    <row r="698" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A698" s="2"/>
       <c r="B698" s="2"/>
     </row>
-    <row r="699" spans="1:2" ht="15.75">
+    <row r="699" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A699" s="2"/>
       <c r="B699" s="2"/>
     </row>
-    <row r="700" spans="1:2" ht="15.75">
+    <row r="700" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A700" s="2"/>
       <c r="B700" s="2"/>
     </row>
-    <row r="701" spans="1:2" ht="15.75">
+    <row r="701" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A701" s="2"/>
       <c r="B701" s="2"/>
     </row>
-    <row r="702" spans="1:2" ht="15.75">
+    <row r="702" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A702" s="2"/>
       <c r="B702" s="2"/>
     </row>
-    <row r="703" spans="1:2" ht="15.75">
+    <row r="703" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A703" s="2"/>
       <c r="B703" s="2"/>
     </row>
-    <row r="704" spans="1:2" ht="15.75">
+    <row r="704" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A704" s="2"/>
       <c r="B704" s="2"/>
     </row>
-    <row r="705" spans="1:2" ht="15.75">
+    <row r="705" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A705" s="2"/>
       <c r="B705" s="2"/>
     </row>
-    <row r="706" spans="1:2" ht="15.75">
+    <row r="706" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A706" s="2"/>
       <c r="B706" s="2"/>
     </row>
-    <row r="707" spans="1:2" ht="15.75">
+    <row r="707" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A707" s="2"/>
       <c r="B707" s="2"/>
     </row>
-    <row r="708" spans="1:2" ht="15.75">
+    <row r="708" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A708" s="2"/>
       <c r="B708" s="2"/>
     </row>
-    <row r="709" spans="1:2" ht="15.75">
+    <row r="709" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A709" s="2"/>
       <c r="B709" s="2"/>
     </row>
-    <row r="710" spans="1:2" ht="15.75">
+    <row r="710" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A710" s="2"/>
       <c r="B710" s="2"/>
     </row>
-    <row r="711" spans="1:2" ht="15.75">
+    <row r="711" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A711" s="2"/>
       <c r="B711" s="2"/>
     </row>
-    <row r="712" spans="1:2" ht="15.75">
+    <row r="712" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A712" s="2"/>
       <c r="B712" s="2"/>
     </row>
-    <row r="713" spans="1:2" ht="15.75">
+    <row r="713" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A713" s="2"/>
       <c r="B713" s="2"/>
     </row>
-    <row r="714" spans="1:2" ht="15.75">
+    <row r="714" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A714" s="2"/>
       <c r="B714" s="2"/>
     </row>
-    <row r="715" spans="1:2" ht="15.75">
+    <row r="715" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A715" s="2"/>
       <c r="B715" s="2"/>
     </row>
-    <row r="716" spans="1:2" ht="15.75">
+    <row r="716" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A716" s="2"/>
       <c r="B716" s="2"/>
     </row>
-    <row r="717" spans="1:2" ht="15.75">
+    <row r="717" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A717" s="2"/>
       <c r="B717" s="2"/>
     </row>
-    <row r="718" spans="1:2" ht="15.75">
+    <row r="718" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A718" s="2"/>
       <c r="B718" s="2"/>
     </row>
-    <row r="719" spans="1:2" ht="15.75">
+    <row r="719" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A719" s="2"/>
       <c r="B719" s="2"/>
     </row>
-    <row r="720" spans="1:2" ht="15.75">
+    <row r="720" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A720" s="2"/>
       <c r="B720" s="2"/>
     </row>
-    <row r="721" spans="1:2" ht="15.75">
+    <row r="721" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A721" s="2"/>
       <c r="B721" s="2"/>
     </row>
-    <row r="722" spans="1:2" ht="15.75">
+    <row r="722" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A722" s="2"/>
       <c r="B722" s="2"/>
     </row>
-    <row r="723" spans="1:2" ht="15.75">
+    <row r="723" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A723" s="2"/>
       <c r="B723" s="2"/>
     </row>
-    <row r="724" spans="1:2" ht="15.75">
+    <row r="724" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A724" s="2"/>
       <c r="B724" s="2"/>
     </row>
-    <row r="725" spans="1:2" ht="15.75">
+    <row r="725" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A725" s="2"/>
       <c r="B725" s="2"/>
     </row>
-    <row r="726" spans="1:2" ht="15.75">
+    <row r="726" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A726" s="2"/>
       <c r="B726" s="2"/>
     </row>
-    <row r="727" spans="1:2" ht="15.75">
+    <row r="727" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A727" s="2"/>
       <c r="B727" s="2"/>
     </row>
-    <row r="728" spans="1:2" ht="15.75">
+    <row r="728" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A728" s="2"/>
       <c r="B728" s="2"/>
     </row>
-    <row r="729" spans="1:2" ht="15.75">
+    <row r="729" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A729" s="2"/>
       <c r="B729" s="2"/>
     </row>
-    <row r="730" spans="1:2" ht="15.75">
+    <row r="730" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A730" s="2"/>
       <c r="B730" s="2"/>
     </row>
-    <row r="731" spans="1:2" ht="15.75">
+    <row r="731" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A731" s="2"/>
       <c r="B731" s="2"/>
     </row>
-    <row r="732" spans="1:2" ht="15.75">
+    <row r="732" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A732" s="2"/>
       <c r="B732" s="2"/>
     </row>
-    <row r="733" spans="1:2" ht="15.75">
+    <row r="733" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A733" s="2"/>
       <c r="B733" s="2"/>
     </row>
-    <row r="734" spans="1:2" ht="15.75">
+    <row r="734" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A734" s="2"/>
       <c r="B734" s="2"/>
     </row>
-    <row r="735" spans="1:2" ht="15.75">
+    <row r="735" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A735" s="2"/>
       <c r="B735" s="2"/>
     </row>
-    <row r="736" spans="1:2" ht="15.75">
+    <row r="736" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A736" s="2"/>
       <c r="B736" s="2"/>
     </row>
-    <row r="737" spans="1:2" ht="15.75">
+    <row r="737" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A737" s="2"/>
       <c r="B737" s="2"/>
     </row>
-    <row r="738" spans="1:2" ht="15.75">
+    <row r="738" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A738" s="2"/>
       <c r="B738" s="2"/>
     </row>
-    <row r="739" spans="1:2" ht="15.75">
+    <row r="739" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A739" s="2"/>
       <c r="B739" s="2"/>
     </row>
-    <row r="740" spans="1:2" ht="15.75">
+    <row r="740" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A740" s="2"/>
       <c r="B740" s="2"/>
     </row>
-    <row r="741" spans="1:2" ht="15.75">
+    <row r="741" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A741" s="2"/>
       <c r="B741" s="2"/>
     </row>
-    <row r="742" spans="1:2" ht="15.75">
+    <row r="742" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A742" s="2"/>
       <c r="B742" s="2"/>
     </row>
-    <row r="743" spans="1:2" ht="15.75">
+    <row r="743" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A743" s="2"/>
       <c r="B743" s="2"/>
     </row>
-    <row r="744" spans="1:2" ht="15.75">
+    <row r="744" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A744" s="2"/>
       <c r="B744" s="2"/>
     </row>
-    <row r="745" spans="1:2" ht="15.75">
+    <row r="745" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A745" s="2"/>
       <c r="B745" s="2"/>
     </row>
-    <row r="746" spans="1:2" ht="15.75">
+    <row r="746" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A746" s="2"/>
       <c r="B746" s="2"/>
     </row>
-    <row r="747" spans="1:2" ht="15.75">
+    <row r="747" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A747" s="2"/>
       <c r="B747" s="2"/>
     </row>
-    <row r="748" spans="1:2" ht="15.75">
+    <row r="748" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A748" s="2"/>
       <c r="B748" s="2"/>
     </row>
-    <row r="749" spans="1:2" ht="15.75">
+    <row r="749" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A749" s="2"/>
       <c r="B749" s="2"/>
     </row>
-    <row r="750" spans="1:2" ht="15.75">
+    <row r="750" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A750" s="2"/>
       <c r="B750" s="2"/>
     </row>
-    <row r="751" spans="1:2" ht="15.75">
+    <row r="751" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A751" s="2"/>
       <c r="B751" s="2"/>
     </row>
-    <row r="752" spans="1:2" ht="15.75">
+    <row r="752" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A752" s="2"/>
       <c r="B752" s="2"/>
     </row>
-    <row r="753" spans="1:2" ht="15.75">
+    <row r="753" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A753" s="2"/>
       <c r="B753" s="2"/>
     </row>
-    <row r="754" spans="1:2" ht="15.75">
+    <row r="754" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A754" s="2"/>
       <c r="B754" s="2"/>
     </row>
-    <row r="755" spans="1:2" ht="15.75">
+    <row r="755" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A755" s="2"/>
       <c r="B755" s="2"/>
     </row>
-    <row r="756" spans="1:2" ht="15.75">
+    <row r="756" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A756" s="2"/>
       <c r="B756" s="2"/>
     </row>
-    <row r="757" spans="1:2" ht="15.75">
+    <row r="757" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A757" s="2"/>
       <c r="B757" s="2"/>
     </row>
-    <row r="758" spans="1:2" ht="15.75">
+    <row r="758" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A758" s="2"/>
       <c r="B758" s="2"/>
     </row>
-    <row r="759" spans="1:2" ht="15.75">
+    <row r="759" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A759" s="2"/>
       <c r="B759" s="2"/>
     </row>
-    <row r="760" spans="1:2" ht="15.75">
+    <row r="760" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A760" s="2"/>
       <c r="B760" s="2"/>
     </row>
-    <row r="761" spans="1:2" ht="15.75">
+    <row r="761" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A761" s="2"/>
       <c r="B761" s="2"/>
     </row>
-    <row r="762" spans="1:2" ht="15.75">
+    <row r="762" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A762" s="2"/>
-      <c r="B762" s="1"/>
-    </row>
-    <row r="763" spans="1:2" ht="15.75">
+      <c r="B762" s="2"/>
+    </row>
+    <row r="763" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A763" s="2"/>
       <c r="B763" s="1"/>
     </row>
-    <row r="764" spans="1:2" ht="15.75">
+    <row r="764" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A764" s="2"/>
       <c r="B764" s="1"/>
     </row>
-    <row r="765" spans="1:2" ht="15.75">
+    <row r="765" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A765" s="2"/>
       <c r="B765" s="1"/>
     </row>
-    <row r="766" spans="1:2" ht="15.75">
+    <row r="766" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A766" s="2"/>
       <c r="B766" s="1"/>
     </row>
-    <row r="767" spans="1:2" ht="15.75">
+    <row r="767" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A767" s="2"/>
       <c r="B767" s="1"/>
     </row>
-    <row r="768" spans="1:2" ht="15.75">
+    <row r="768" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A768" s="2"/>
       <c r="B768" s="1"/>
     </row>
-    <row r="769" spans="1:2" ht="15.75">
+    <row r="769" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A769" s="2"/>
       <c r="B769" s="1"/>
     </row>
-    <row r="770" spans="1:2" ht="15.75">
+    <row r="770" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A770" s="2"/>
       <c r="B770" s="1"/>
     </row>
-    <row r="771" spans="1:2" ht="15.75">
+    <row r="771" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A771" s="2"/>
       <c r="B771" s="1"/>
     </row>
-    <row r="772" spans="1:2" ht="15.75">
+    <row r="772" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A772" s="2"/>
       <c r="B772" s="1"/>
     </row>
-    <row r="773" spans="1:2" ht="15.75">
+    <row r="773" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A773" s="2"/>
       <c r="B773" s="1"/>
     </row>
-    <row r="774" spans="1:2" ht="15.75">
+    <row r="774" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A774" s="2"/>
       <c r="B774" s="1"/>
     </row>
-    <row r="775" spans="1:2" ht="15.75">
+    <row r="775" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A775" s="2"/>
       <c r="B775" s="1"/>
     </row>
-    <row r="776" spans="1:2" ht="15.75">
+    <row r="776" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A776" s="2"/>
       <c r="B776" s="1"/>
     </row>
-    <row r="777" spans="1:2" ht="15.75">
+    <row r="777" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A777" s="2"/>
       <c r="B777" s="1"/>
     </row>
-    <row r="778" spans="1:2" ht="15.75">
+    <row r="778" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A778" s="2"/>
       <c r="B778" s="1"/>
     </row>
-    <row r="779" spans="1:2" ht="15.75">
+    <row r="779" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A779" s="2"/>
       <c r="B779" s="1"/>
     </row>
-    <row r="780" spans="1:2" ht="15.75">
+    <row r="780" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A780" s="2"/>
       <c r="B780" s="1"/>
     </row>
-    <row r="781" spans="1:2" ht="15.75">
+    <row r="781" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A781" s="2"/>
       <c r="B781" s="1"/>
     </row>
-    <row r="782" spans="1:2" ht="15.75">
+    <row r="782" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A782" s="2"/>
       <c r="B782" s="1"/>
     </row>
-    <row r="783" spans="1:2" ht="15.75">
+    <row r="783" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A783" s="2"/>
       <c r="B783" s="1"/>
     </row>
-    <row r="784" spans="1:2" ht="15.75">
+    <row r="784" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A784" s="2"/>
       <c r="B784" s="1"/>
     </row>
-    <row r="785" spans="1:2" ht="15.75">
+    <row r="785" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A785" s="2"/>
       <c r="B785" s="1"/>
     </row>
-    <row r="786" spans="1:2" ht="15.75">
+    <row r="786" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A786" s="2"/>
       <c r="B786" s="1"/>
     </row>
-    <row r="787" spans="1:2" ht="15.75">
+    <row r="787" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A787" s="2"/>
       <c r="B787" s="1"/>
     </row>
-    <row r="788" spans="1:2" ht="15.75">
+    <row r="788" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A788" s="2"/>
       <c r="B788" s="1"/>
     </row>
-    <row r="789" spans="1:2" ht="15.75">
+    <row r="789" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A789" s="2"/>
       <c r="B789" s="1"/>
     </row>
-    <row r="790" spans="1:2" ht="15.75">
+    <row r="790" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A790" s="2"/>
       <c r="B790" s="1"/>
     </row>
-    <row r="791" spans="1:2" ht="15.75">
+    <row r="791" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A791" s="2"/>
       <c r="B791" s="1"/>
     </row>
-    <row r="792" spans="1:2" ht="15.75">
+    <row r="792" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A792" s="2"/>
       <c r="B792" s="1"/>
     </row>
-    <row r="793" spans="1:2" ht="15.75">
+    <row r="793" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A793" s="2"/>
       <c r="B793" s="1"/>
     </row>
-    <row r="794" spans="1:2" ht="15.75">
+    <row r="794" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A794" s="2"/>
       <c r="B794" s="1"/>
     </row>
-    <row r="795" spans="1:2" ht="15.75">
+    <row r="795" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A795" s="2"/>
       <c r="B795" s="1"/>
     </row>
-    <row r="796" spans="1:2" ht="15.75">
+    <row r="796" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A796" s="2"/>
       <c r="B796" s="1"/>
     </row>
-    <row r="797" spans="1:2" ht="15.75">
+    <row r="797" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A797" s="2"/>
       <c r="B797" s="1"/>
     </row>
-    <row r="798" spans="1:2" ht="15.75">
+    <row r="798" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A798" s="2"/>
       <c r="B798" s="1"/>
     </row>
-    <row r="799" spans="1:2" ht="15.75">
+    <row r="799" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A799" s="2"/>
       <c r="B799" s="1"/>
     </row>
-    <row r="800" spans="1:2" ht="15.75">
+    <row r="800" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A800" s="2"/>
       <c r="B800" s="1"/>
     </row>
-    <row r="801" spans="1:2" ht="15.75">
+    <row r="801" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A801" s="2"/>
       <c r="B801" s="1"/>
     </row>
-    <row r="802" spans="1:2" ht="15.75">
+    <row r="802" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A802" s="2"/>
       <c r="B802" s="1"/>
     </row>
-    <row r="803" spans="1:2" ht="15.75">
+    <row r="803" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A803" s="2"/>
       <c r="B803" s="1"/>
     </row>
-    <row r="804" spans="1:2" ht="15.75">
+    <row r="804" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A804" s="2"/>
       <c r="B804" s="1"/>
     </row>
-    <row r="805" spans="1:2" ht="15.75">
+    <row r="805" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A805" s="2"/>
       <c r="B805" s="1"/>
     </row>
-    <row r="806" spans="1:2" ht="15.75">
+    <row r="806" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A806" s="2"/>
       <c r="B806" s="1"/>
     </row>
-    <row r="807" spans="1:2" ht="15.75">
+    <row r="807" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A807" s="2"/>
       <c r="B807" s="1"/>
     </row>
-    <row r="808" spans="1:2" ht="15.75">
+    <row r="808" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A808" s="2"/>
       <c r="B808" s="1"/>
     </row>
-    <row r="809" spans="1:2" ht="15.75">
+    <row r="809" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A809" s="2"/>
       <c r="B809" s="1"/>
     </row>
-    <row r="810" spans="1:2" ht="15.75">
+    <row r="810" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A810" s="2"/>
       <c r="B810" s="1"/>
     </row>
-    <row r="811" spans="1:2" ht="15.75">
+    <row r="811" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A811" s="2"/>
       <c r="B811" s="1"/>
     </row>
-    <row r="812" spans="1:2" ht="15.75">
+    <row r="812" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A812" s="2"/>
       <c r="B812" s="1"/>
     </row>
-    <row r="813" spans="1:2" ht="15.75">
+    <row r="813" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A813" s="2"/>
       <c r="B813" s="1"/>
     </row>
-    <row r="814" spans="1:2" ht="15.75">
+    <row r="814" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A814" s="2"/>
       <c r="B814" s="1"/>
     </row>
-    <row r="815" spans="1:2" ht="15.75">
+    <row r="815" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A815" s="2"/>
       <c r="B815" s="1"/>
     </row>
-    <row r="816" spans="1:2" ht="15.75">
+    <row r="816" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A816" s="2"/>
       <c r="B816" s="1"/>
     </row>
-    <row r="817" spans="1:2" ht="15.75">
+    <row r="817" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A817" s="2"/>
       <c r="B817" s="1"/>
     </row>
-    <row r="818" spans="1:2" ht="15.75">
+    <row r="818" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A818" s="2"/>
       <c r="B818" s="1"/>
     </row>
-    <row r="819" spans="1:2" ht="15.75">
+    <row r="819" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A819" s="2"/>
       <c r="B819" s="1"/>
     </row>
-    <row r="820" spans="1:2" ht="15.75">
+    <row r="820" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A820" s="2"/>
       <c r="B820" s="1"/>
     </row>
-    <row r="821" spans="1:2" ht="15.75">
+    <row r="821" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A821" s="2"/>
       <c r="B821" s="1"/>
     </row>
-    <row r="822" spans="1:2" ht="15.75">
+    <row r="822" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A822" s="2"/>
       <c r="B822" s="1"/>
     </row>
-    <row r="823" spans="1:2" ht="15.75">
+    <row r="823" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A823" s="2"/>
       <c r="B823" s="1"/>
     </row>
-    <row r="824" spans="1:2" ht="15.75">
+    <row r="824" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A824" s="2"/>
       <c r="B824" s="1"/>
     </row>
-    <row r="825" spans="1:2" ht="15.75">
+    <row r="825" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A825" s="2"/>
       <c r="B825" s="1"/>
     </row>
-    <row r="826" spans="1:2" ht="15.75">
+    <row r="826" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A826" s="2"/>
       <c r="B826" s="1"/>
     </row>
-    <row r="827" spans="1:2" ht="15.75">
+    <row r="827" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A827" s="2"/>
       <c r="B827" s="1"/>
     </row>
-    <row r="828" spans="1:2" ht="15.75">
+    <row r="828" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A828" s="2"/>
       <c r="B828" s="1"/>
     </row>
-    <row r="829" spans="1:2" ht="15.75">
+    <row r="829" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A829" s="2"/>
       <c r="B829" s="1"/>
     </row>
-    <row r="830" spans="1:2" ht="15.75">
-      <c r="A830" s="1"/>
+    <row r="830" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A830" s="2"/>
       <c r="B830" s="1"/>
     </row>
-    <row r="831" spans="1:2" ht="15.75">
+    <row r="831" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
     </row>
-    <row r="832" spans="1:2" ht="15.75">
+    <row r="832" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
     </row>
-    <row r="833" spans="1:2" ht="15.75">
+    <row r="833" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
     </row>
-    <row r="834" spans="1:2" ht="15.75">
+    <row r="834" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
     </row>
-    <row r="835" spans="1:2" ht="15.75">
+    <row r="835" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
     </row>
-    <row r="836" spans="1:2" ht="15.75">
+    <row r="836" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
     </row>
-    <row r="837" spans="1:2" ht="15.75">
+    <row r="837" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
     </row>
-    <row r="838" spans="1:2" ht="15.75">
+    <row r="838" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
     </row>
-    <row r="839" spans="1:2" ht="15.75">
+    <row r="839" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
     </row>
-    <row r="840" spans="1:2" ht="15.75">
+    <row r="840" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
     </row>
-    <row r="841" spans="1:2" ht="15.75">
+    <row r="841" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
     </row>
-    <row r="842" spans="1:2" ht="15.75">
+    <row r="842" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
     </row>
-    <row r="843" spans="1:2" ht="15.75">
+    <row r="843" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
     </row>
-    <row r="844" spans="1:2" ht="15.75">
+    <row r="844" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
     </row>
-    <row r="845" spans="1:2" ht="15.75">
+    <row r="845" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
     </row>
-    <row r="846" spans="1:2" ht="15.75">
+    <row r="846" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
     </row>
-    <row r="847" spans="1:2" ht="15.75">
+    <row r="847" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
     </row>
-    <row r="848" spans="1:2" ht="15.75">
+    <row r="848" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
     </row>
-    <row r="849" spans="1:2" ht="15.75">
+    <row r="849" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
     </row>
-    <row r="850" spans="1:2" ht="15.75">
+    <row r="850" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
     </row>
-    <row r="851" spans="1:2" ht="15.75">
+    <row r="851" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
     </row>
-    <row r="852" spans="1:2" ht="15.75">
+    <row r="852" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
     </row>
-    <row r="853" spans="1:2" ht="15.75">
+    <row r="853" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
     </row>
-    <row r="854" spans="1:2" ht="15.75">
+    <row r="854" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
     </row>
-    <row r="855" spans="1:2" ht="15.75">
+    <row r="855" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
     </row>
-    <row r="856" spans="1:2" ht="15.75">
+    <row r="856" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
     </row>
-    <row r="857" spans="1:2" ht="15.75">
+    <row r="857" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
     </row>
-    <row r="858" spans="1:2" ht="15.75">
+    <row r="858" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
     </row>
-    <row r="859" spans="1:2" ht="15.75">
+    <row r="859" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
     </row>
-    <row r="860" spans="1:2" ht="15.75">
+    <row r="860" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
     </row>
-    <row r="861" spans="1:2" ht="15.75">
+    <row r="861" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
     </row>
-    <row r="862" spans="1:2" ht="15.75">
+    <row r="862" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
     </row>
-    <row r="863" spans="1:2" ht="15.75">
+    <row r="863" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
     </row>
-    <row r="864" spans="1:2" ht="15.75">
+    <row r="864" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
     </row>
-    <row r="865" spans="1:2" ht="15.75">
+    <row r="865" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
     </row>
-    <row r="866" spans="1:2" ht="15.75">
+    <row r="866" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
     </row>
-    <row r="867" spans="1:2" ht="15.75">
+    <row r="867" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
     </row>
-    <row r="868" spans="1:2" ht="15.75">
+    <row r="868" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
     </row>
-    <row r="869" spans="1:2" ht="15.75">
+    <row r="869" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
     </row>
-    <row r="870" spans="1:2" ht="15.75">
+    <row r="870" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
     </row>
-    <row r="871" spans="1:2" ht="15.75">
+    <row r="871" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
     </row>
-    <row r="872" spans="1:2" ht="15.75">
+    <row r="872" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
     </row>
-    <row r="873" spans="1:2" ht="15.75">
+    <row r="873" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
     </row>
-    <row r="874" spans="1:2" ht="15.75">
+    <row r="874" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
     </row>
-    <row r="875" spans="1:2" ht="15.75">
+    <row r="875" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
     </row>
-    <row r="876" spans="1:2" ht="15.75">
+    <row r="876" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
     </row>
-    <row r="877" spans="1:2" ht="15.75">
+    <row r="877" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
     </row>
-    <row r="878" spans="1:2" ht="15.75">
+    <row r="878" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
     </row>
-    <row r="879" spans="1:2" ht="15.75">
+    <row r="879" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
     </row>
-    <row r="880" spans="1:2" ht="15.75">
+    <row r="880" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
     </row>
-    <row r="881" spans="1:2" ht="15.75">
+    <row r="881" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
     </row>
-    <row r="882" spans="1:2" ht="15.75">
+    <row r="882" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
     </row>
-    <row r="883" spans="1:2" ht="15.75">
+    <row r="883" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
     </row>
-    <row r="884" spans="1:2" ht="15.75">
+    <row r="884" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
     </row>
-    <row r="885" spans="1:2" ht="15.75">
+    <row r="885" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
     </row>
-    <row r="886" spans="1:2" ht="15.75">
+    <row r="886" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
     </row>
-    <row r="887" spans="1:2" ht="15.75">
+    <row r="887" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
     </row>
-    <row r="888" spans="1:2" ht="15.75">
+    <row r="888" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
     </row>
-    <row r="889" spans="1:2" ht="15.75">
+    <row r="889" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
     </row>
-    <row r="890" spans="1:2" ht="15.75">
+    <row r="890" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
     </row>
-    <row r="891" spans="1:2" ht="15.75">
+    <row r="891" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
     </row>
-    <row r="892" spans="1:2" ht="15.75">
+    <row r="892" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
     </row>
-    <row r="893" spans="1:2" ht="15.75">
+    <row r="893" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
     </row>
-    <row r="894" spans="1:2" ht="15.75">
+    <row r="894" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
     </row>
-    <row r="895" spans="1:2" ht="15.75">
+    <row r="895" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
     </row>
-    <row r="896" spans="1:2" ht="15.75">
+    <row r="896" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
     </row>
-    <row r="897" spans="1:2" ht="15.75">
+    <row r="897" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
     </row>
-    <row r="898" spans="1:2" ht="15.75">
+    <row r="898" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
     </row>
-    <row r="899" spans="1:2" ht="15.75">
+    <row r="899" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
     </row>
-    <row r="900" spans="1:2" ht="15.75">
+    <row r="900" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
     </row>
-    <row r="901" spans="1:2" ht="15.75">
+    <row r="901" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
     </row>
-    <row r="902" spans="1:2" ht="15.75">
+    <row r="902" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
     </row>
-    <row r="903" spans="1:2" ht="15.75">
+    <row r="903" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
     </row>
-    <row r="904" spans="1:2" ht="15.75">
+    <row r="904" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
     </row>
-    <row r="905" spans="1:2" ht="15.75">
+    <row r="905" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
     </row>
-    <row r="906" spans="1:2" ht="15.75">
+    <row r="906" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
     </row>
-    <row r="907" spans="1:2" ht="15.75">
+    <row r="907" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
     </row>
-    <row r="908" spans="1:2" ht="15.75">
+    <row r="908" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
     </row>
-    <row r="909" spans="1:2" ht="15.75">
+    <row r="909" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
     </row>
-    <row r="910" spans="1:2" ht="15.75">
+    <row r="910" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
     </row>
-    <row r="911" spans="1:2" ht="15.75">
+    <row r="911" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
     </row>
-    <row r="912" spans="1:2" ht="15.75">
+    <row r="912" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
     </row>
-    <row r="913" spans="1:2" ht="15.75">
+    <row r="913" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
     </row>
-    <row r="914" spans="1:2" ht="15.75">
+    <row r="914" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
     </row>
-    <row r="915" spans="1:2" ht="15.75">
+    <row r="915" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
     </row>
-    <row r="916" spans="1:2" ht="15.75">
+    <row r="916" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
     </row>
-    <row r="917" spans="1:2" ht="15.75">
+    <row r="917" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
     </row>
-    <row r="918" spans="1:2" ht="15.75">
+    <row r="918" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
     </row>
-    <row r="919" spans="1:2" ht="15.75">
+    <row r="919" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
     </row>
-    <row r="920" spans="1:2" ht="15.75">
+    <row r="920" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
     </row>
-    <row r="921" spans="1:2" ht="15.75">
+    <row r="921" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
     </row>
-    <row r="922" spans="1:2" ht="15.75">
+    <row r="922" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
     </row>
-    <row r="923" spans="1:2" ht="15.75">
+    <row r="923" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
     </row>
-    <row r="924" spans="1:2" ht="15.75">
+    <row r="924" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
     </row>
-    <row r="925" spans="1:2" ht="15.75">
+    <row r="925" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
     </row>
-    <row r="926" spans="1:2" ht="15.75">
+    <row r="926" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
     </row>
-    <row r="927" spans="1:2" ht="15.75">
+    <row r="927" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
     </row>
-    <row r="928" spans="1:2" ht="15.75">
+    <row r="928" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
     </row>
-    <row r="929" spans="1:2" ht="15.75">
+    <row r="929" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
     </row>
-    <row r="930" spans="1:2" ht="15.75">
+    <row r="930" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
     </row>
-    <row r="931" spans="1:2" ht="15.75">
+    <row r="931" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
     </row>
-    <row r="932" spans="1:2" ht="15.75">
+    <row r="932" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
     </row>
-    <row r="933" spans="1:2" ht="15.75">
+    <row r="933" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
     </row>
-    <row r="934" spans="1:2" ht="15.75">
+    <row r="934" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
     </row>
-    <row r="935" spans="1:2" ht="15.75">
+    <row r="935" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
     </row>
-    <row r="936" spans="1:2" ht="15.75">
+    <row r="936" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
     </row>
-    <row r="937" spans="1:2" ht="15.75">
+    <row r="937" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
     </row>
-    <row r="938" spans="1:2" ht="15.75">
+    <row r="938" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
     </row>
-    <row r="939" spans="1:2" ht="15.75">
+    <row r="939" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
     </row>
-    <row r="940" spans="1:2" ht="15.75">
+    <row r="940" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
     </row>
-    <row r="941" spans="1:2" ht="15.75">
+    <row r="941" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
     </row>
-    <row r="942" spans="1:2" ht="15.75">
+    <row r="942" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
     </row>
-    <row r="943" spans="1:2" ht="15.75">
+    <row r="943" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
     </row>
-    <row r="944" spans="1:2" ht="15.75">
+    <row r="944" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
     </row>
-    <row r="945" spans="1:2" ht="15.75">
+    <row r="945" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
     </row>
-    <row r="946" spans="1:2" ht="15.75">
+    <row r="946" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
     </row>
-    <row r="947" spans="1:2" ht="15.75">
+    <row r="947" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
     </row>
-    <row r="948" spans="1:2" ht="15.75">
+    <row r="948" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
     </row>
-    <row r="949" spans="1:2" ht="15.75">
+    <row r="949" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
     </row>
-    <row r="950" spans="1:2" ht="15.75">
+    <row r="950" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
     </row>
-    <row r="951" spans="1:2" ht="15.75">
+    <row r="951" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
     </row>
-    <row r="952" spans="1:2" ht="15.75">
+    <row r="952" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
     </row>
-    <row r="953" spans="1:2" ht="15.75">
+    <row r="953" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
     </row>
-    <row r="954" spans="1:2" ht="15.75">
+    <row r="954" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
     </row>
-    <row r="955" spans="1:2" ht="15.75">
+    <row r="955" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
     </row>
-    <row r="956" spans="1:2" ht="15.75">
+    <row r="956" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
     </row>
-    <row r="957" spans="1:2" ht="15.75">
+    <row r="957" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
     </row>
-    <row r="958" spans="1:2" ht="15.75">
+    <row r="958" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
     </row>
-    <row r="959" spans="1:2" ht="15.75">
+    <row r="959" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
     </row>
-    <row r="960" spans="1:2" ht="15.75">
+    <row r="960" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
     </row>
-    <row r="961" spans="1:2" ht="15.75">
+    <row r="961" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
     </row>
-    <row r="962" spans="1:2" ht="15.75">
+    <row r="962" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
     </row>
-    <row r="963" spans="1:2" ht="15.75">
+    <row r="963" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
     </row>
-    <row r="964" spans="1:2" ht="15.75">
+    <row r="964" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
     </row>
-    <row r="965" spans="1:2" ht="15.75">
+    <row r="965" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
     </row>
-    <row r="966" spans="1:2" ht="15.75">
+    <row r="966" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
     </row>
-    <row r="967" spans="1:2" ht="15.75">
+    <row r="967" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
     </row>
-    <row r="968" spans="1:2" ht="15.75">
+    <row r="968" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
     </row>
-    <row r="969" spans="1:2" ht="15.75">
+    <row r="969" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
     </row>
-    <row r="970" spans="1:2" ht="15.75">
+    <row r="970" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
     </row>
-    <row r="971" spans="1:2" ht="15.75">
+    <row r="971" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
     </row>
-    <row r="972" spans="1:2" ht="15.75">
+    <row r="972" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
     </row>
-    <row r="973" spans="1:2" ht="15.75">
+    <row r="973" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
     </row>
-    <row r="974" spans="1:2" ht="15.75">
+    <row r="974" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
     </row>
-    <row r="975" spans="1:2" ht="15.75">
+    <row r="975" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
     </row>
-    <row r="976" spans="1:2" ht="15.75">
+    <row r="976" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
     </row>
-    <row r="977" spans="1:2" ht="15.75">
+    <row r="977" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
     </row>
-    <row r="978" spans="1:2" ht="15.75">
+    <row r="978" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
     </row>
-    <row r="979" spans="1:2" ht="15.75">
+    <row r="979" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
     </row>
-    <row r="980" spans="1:2" ht="15.75">
+    <row r="980" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
     </row>
-    <row r="981" spans="1:2" ht="15.75">
+    <row r="981" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
     </row>
-    <row r="982" spans="1:2" ht="15.75">
+    <row r="982" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
     </row>
-    <row r="983" spans="1:2" ht="15.75">
+    <row r="983" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
     </row>
-    <row r="984" spans="1:2" ht="15.75">
+    <row r="984" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
     </row>
-    <row r="985" spans="1:2" ht="15.75">
+    <row r="985" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A985" s="1"/>
       <c r="B985" s="1"/>
     </row>
-    <row r="986" spans="1:2" ht="15.75">
+    <row r="986" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A986" s="1"/>
       <c r="B986" s="1"/>
     </row>
-    <row r="987" spans="1:2" ht="15.75">
+    <row r="987" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A987" s="1"/>
       <c r="B987" s="1"/>
     </row>
-    <row r="988" spans="1:2" ht="15.75">
+    <row r="988" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A988" s="1"/>
       <c r="B988" s="1"/>
     </row>
-    <row r="989" spans="1:2" ht="15.75">
+    <row r="989" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A989" s="1"/>
       <c r="B989" s="1"/>
     </row>
-    <row r="990" spans="1:2" ht="15.75">
+    <row r="990" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A990" s="1"/>
       <c r="B990" s="1"/>
     </row>
-    <row r="991" spans="1:2" ht="15.75">
+    <row r="991" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A991" s="1"/>
       <c r="B991" s="1"/>
     </row>
-    <row r="992" spans="1:2" ht="15.75">
+    <row r="992" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A992" s="1"/>
       <c r="B992" s="1"/>
     </row>
-    <row r="993" spans="1:2" ht="15.75">
+    <row r="993" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A993" s="1"/>
       <c r="B993" s="1"/>
     </row>
-    <row r="994" spans="1:2" ht="15.75">
+    <row r="994" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A994" s="1"/>
       <c r="B994" s="1"/>
     </row>
-    <row r="995" spans="1:2" ht="15.75">
+    <row r="995" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A995" s="1"/>
       <c r="B995" s="1"/>
     </row>
-    <row r="996" spans="1:2" ht="15.75">
+    <row r="996" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A996" s="1"/>
       <c r="B996" s="1"/>
     </row>
-    <row r="997" spans="1:2" ht="15.75">
+    <row r="997" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A997" s="1"/>
       <c r="B997" s="1"/>
     </row>
-    <row r="998" spans="1:2" ht="15.75">
+    <row r="998" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A998" s="1"/>
       <c r="B998" s="1"/>
     </row>
-    <row r="999" spans="1:2" ht="15.75">
+    <row r="999" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A999" s="1"/>
       <c r="B999" s="1"/>
     </row>
-    <row r="1000" spans="1:2" ht="15.75">
+    <row r="1000" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1000" s="1"/>
       <c r="B1000" s="1"/>
     </row>
-    <row r="1001" spans="1:2" ht="15.75">
+    <row r="1001" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1001" s="1"/>
       <c r="B1001" s="1"/>
     </row>
-    <row r="1002" spans="1:2" ht="15.75">
+    <row r="1002" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1002" s="1"/>
       <c r="B1002" s="1"/>
     </row>
-    <row r="1003" spans="1:2" ht="15.75">
+    <row r="1003" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1003" s="1"/>
       <c r="B1003" s="1"/>
     </row>
-    <row r="1004" spans="1:2" ht="15.75">
+    <row r="1004" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1004" s="1"/>
       <c r="B1004" s="1"/>
     </row>
-    <row r="1005" spans="1:2" ht="15.75">
+    <row r="1005" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1005" s="1"/>
       <c r="B1005" s="1"/>
     </row>
-    <row r="1006" spans="1:2" ht="15.75">
+    <row r="1006" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1006" s="1"/>
       <c r="B1006" s="1"/>
     </row>
-    <row r="1007" spans="1:2" ht="15.75">
+    <row r="1007" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1007" s="1"/>
       <c r="B1007" s="1"/>
     </row>
-    <row r="1008" spans="1:2" ht="15.75">
+    <row r="1008" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1008" s="1"/>
       <c r="B1008" s="1"/>
     </row>
-    <row r="1009" spans="1:2" ht="15.75">
+    <row r="1009" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1009" s="1"/>
       <c r="B1009" s="1"/>
     </row>
-    <row r="1010" spans="1:2" ht="15.75">
+    <row r="1010" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1010" s="1"/>
       <c r="B1010" s="1"/>
     </row>
-    <row r="1011" spans="1:2" ht="15.75">
+    <row r="1011" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1011" s="1"/>
       <c r="B1011" s="1"/>
     </row>
-    <row r="1012" spans="1:2" ht="15.75">
+    <row r="1012" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1012" s="1"/>
       <c r="B1012" s="1"/>
     </row>
-    <row r="1013" spans="1:2" ht="15.75">
+    <row r="1013" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1013" s="1"/>
       <c r="B1013" s="1"/>
     </row>
-    <row r="1014" spans="1:2" ht="15.75">
+    <row r="1014" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1014" s="1"/>
       <c r="B1014" s="1"/>
     </row>
-    <row r="1015" spans="1:2" ht="15.75">
+    <row r="1015" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1015" s="1"/>
       <c r="B1015" s="1"/>
     </row>
-    <row r="1016" spans="1:2" ht="15.75">
+    <row r="1016" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1016" s="1"/>
       <c r="B1016" s="1"/>
     </row>
-    <row r="1017" spans="1:2" ht="15.75">
+    <row r="1017" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1017" s="1"/>
       <c r="B1017" s="1"/>
     </row>
-    <row r="1018" spans="1:2" ht="15.75">
+    <row r="1018" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1018" s="1"/>
       <c r="B1018" s="1"/>
     </row>
-    <row r="1019" spans="1:2" ht="15.75">
+    <row r="1019" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1019" s="1"/>
       <c r="B1019" s="1"/>
     </row>
-    <row r="1020" spans="1:2" ht="15.75">
+    <row r="1020" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1020" s="1"/>
       <c r="B1020" s="1"/>
     </row>
-    <row r="1021" spans="1:2" ht="15.75">
+    <row r="1021" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1021" s="1"/>
       <c r="B1021" s="1"/>
     </row>
-    <row r="1022" spans="1:2" ht="15.75">
+    <row r="1022" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1022" s="1"/>
       <c r="B1022" s="1"/>
     </row>
-    <row r="1023" spans="1:2" ht="15.75">
+    <row r="1023" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1023" s="1"/>
       <c r="B1023" s="1"/>
     </row>
-    <row r="1024" spans="1:2" ht="15.75">
+    <row r="1024" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1024" s="1"/>
       <c r="B1024" s="1"/>
+    </row>
+    <row r="1025" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1025" s="1"/>
+      <c r="B1025" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dados-catalago-pcm-externo/nomes_usuais.xlsx
+++ b/dados-catalago-pcm-externo/nomes_usuais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecas/dados-catalago-pcm-externo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="108" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28A4B06B-14B7-492E-AA3C-165EBFCAD48F}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37358B64-4CD0-47DB-B59C-9FF9808AADAA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1363,7 +1363,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2853,8 +2855,8 @@
       </c>
     </row>
     <row r="110" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A110" s="5">
-        <v>64262</v>
+      <c r="A110" s="18">
+        <v>1010051726</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>112</v>
@@ -2885,7 +2887,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
         <v>1040077370</v>
       </c>
@@ -2895,8 +2897,9 @@
       <c r="C113" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G113" s="15"/>
+    </row>
+    <row r="114" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
         <v>1040099247</v>
       </c>
@@ -2907,7 +2910,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
         <v>1040100560</v>
       </c>
@@ -2918,7 +2921,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
         <v>1040077399</v>
       </c>
@@ -2929,7 +2932,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
         <v>1040077374</v>
       </c>
@@ -2940,7 +2943,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
         <v>1040077399</v>
       </c>
@@ -2951,7 +2954,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="16">
         <v>1010050632</v>
       </c>
@@ -2962,7 +2965,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
         <v>409250</v>
       </c>
@@ -2973,7 +2976,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
         <v>1010020541</v>
       </c>
@@ -2984,7 +2987,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="5">
         <v>1010020879</v>
       </c>
@@ -2995,7 +2998,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
         <v>1040077380</v>
       </c>
@@ -3006,7 +3009,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="5">
         <v>1010021520</v>
       </c>
@@ -3017,7 +3020,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
         <v>1040098861</v>
       </c>
@@ -3028,7 +3031,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="5">
         <v>1010077261</v>
       </c>
@@ -3039,7 +3042,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
         <v>1010027664</v>
       </c>
@@ -3050,7 +3053,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="5">
         <v>1010083731</v>
       </c>
@@ -5052,7 +5055,6 @@
       <c r="C309" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="F309" s="18"/>
     </row>
     <row r="310" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" s="12">
